--- a/results/local_results.xlsx
+++ b/results/local_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,35 +474,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>## [VOC 분석 보고] 고객 피드백 요약 및 개선 가이드
-**1. 🔍 VOC 1줄 요약 (One-Line Summary)**
-&gt; 콘텐츠 내 성우/더빙의 음질 및 캐릭터 적합성 부족에 대한 불만이 접수됨.
----
-**2. 🛠️ 분석 및 개선 가이드 (Analysis &amp; Action Plan)**
-**① 주요 VOC 키워드 및 원인**
-*   **키워드:** 더빙, 성우, 음성, 목소리
-*   **추정 원인:**
-    *   **음질 문제:** 녹음 상태가 불량하거나 후반 작업(마스터링, 믹싱)이 부실했을 가능성.
-    *   **싱크(싱크로율) 오류:** 대사와 입 모양의 타이밍이 맞지 않아 몰입을 방해하는 경우.
-    *   **캐릭터성 불일치:** 캐릭터 설정(나이, 성별, 톤, 감정 표현)과 실제 성우의 연기 톤이 매칭되지 않는 경우.
-**② 담당 부서별 액션 플랜**
-| 부서 | 담당 내용 (Action Item) | 체크 포인트 |
-| :--- | :--- | :--- |
-| **제작/운영팀** | **QA 루틴 강화:** 더빙/성우 관련 리스크 항목을 QA 체크리스트에 필수 반영. | 단순 '음성 존재 여부'를 넘어 '발음 정확도', '감정 표현의 자연스러움'을 확인하도록 프로세스 개선. |
-| **성우 관리팀** | **사전 커뮤니케이션:** 성우 캐스팅 시, 캐릭터 디렉팅 자료를 상세히 제공하고 리딩 전 세부 피드백 주기. | 클라이언트/기획 의도와 성우가 해석한 내용 사이에 오해가 없는지 초기 단계부터 확인. |
-| **기술/AS팀** | **최종 아웃풋 검수:** 패치 또는 마이너 업데이트 전, 핵심 대사(Key Dialogue) 구간에 대한 사운드 버그 리포팅 체계 구축. | 음성 데이터가 게임 엔진/앱 환경에서 왜 저음/고음으로 변형되는지 등 기술적 결함 여부 점검. |
-**③ 단기 개선 목표 (Goal)**
-*   '짜증나다', '부자연스럽다'와 같은 **감정적 키워드**가 언급되는 더빙 관련 피드백을 **최소 30% 이상 감지하고 개선**하는 것을 목표로 합니다.</t>
+          <t>## 📋 VOC 분석 결과 보고
+**작성자:** 사내 VOC 데이터 분석가
+**분석 일자:** 2024년 X월 X일
+**민원 주제:** 더빙 목소리 품질 관련 불만 제기
+---
+### 📝 1줄 요약 (Summary)
+**더빙(성우)의 목소리 톤, 발성, 또는 전달력 등 표현 품질이 불쾌감을 주어 콘텐츠 경험을 저해한다는 의견임.**
+---
+### 🧭 개선 가이드 (Action Guide)
+해당 민원은 단순한 호불호를 넘어 '콘텐츠 몰입도 저해'라는 사용자 경험(UX) 측면의 문제로 분류될 수 있습니다. 아래 3단계 가이드를 통해 문제를 정의하고 해결 방안을 모색하시기 바랍니다.
+#### 🔎 1단계: 문제 구체화 및 정의 (Diagnosis)
+**👉 목표: 불만이 '어디서' 발생했는지 원인 분석**
+*   **구체적인 맥락 파악:** 해당 민원이 어떤 콘텐츠(작품명, 에피소드)에 대한 것인지, 특정 장면에서만 발생하는 문제인지 확인해야 합니다.
+*   **불만 유형 분류:** 단순히 '싫다'가 아니라, 목소리 자체가 **[저음/고음/톤]** 문제인지, **[발음/발성/억양]** 문제인지, 혹은 캐릭터의 **[감정선/연기력]** 문제인지 구체적으로 재정의해야 합니다. (예: 너무 기계적인 목소리, 부자연스러운 호흡 등)
+*   **타 콘텐츠 비교:** 해당 더빙이 업계 표준이나 유사 콘텐츠 대비 어느 지점에서 부족한지 비교 분석을 시도합니다.
+#### 🛠️ 2단계: 단기적 대응 방안 (Short-term Mitigation)
+**👉 목표: 즉각적인 고객 만족도 개선**
+*   **피드백 전달 및 경청:** VOC 접수 채널을 통해 해당 민원에 대해 정중하게 사과의 뜻을 전달하고, 추가적인 구체적인 의견을 재요청합니다.
+*   **선택지 제공 검토:** 기술적 가능하다면(혹은 이후 업데이트 시) 사용자가 목소리 관련 설정을 조절하거나, 대체 자막 환경을 제공할 수 있는지 검토합니다.
+*   **내부 공유:** 해당 피드백을 성우 기획 및 QC(품질관리) 담당 팀에 즉시 공유하여 인지시키고, 해당 콘텐츠의 리뷰 목록에 등록합니다.
+#### 🚀 3단계: 장기적 개선 방안 (Long-term Solution)
+**👉 목표: 재발 방지 시스템 구축**
+*   **캐스팅 기준 강화:** 성우 캐스팅 전, 작품의 톤앤매너(Tone &amp; Manner)에 대한 상세한 가이드를 제공하고, 다수의 테스트를 통해 캐릭터와 가장 적합한 음색을 가진 배우를 선정하는 프로세스를 강화해야 합니다.
+*   **현장 QC 루프 구축:** 녹음 후 최종 검토 단계에서 단순히 '기술적 오류'만 체크하는 것이 아니라, 일반 시청자 관점에서 **'몰입도'** 및 **'자연스러움'** 측면의 QC 체크리스트를 도입하고 점수를 부여하는 시스템을 구축해야 합니다.
+*   **사전 리스크 관리:** 주요 작품의 성우 기용 시, 사전 시범 녹음(테스트 트랙)을 통해 잠재적인 부작용(성우의 이질감, 톤 불일치 등)을 미리 발굴할 수 있는 사전 검토 단계를 의무화합니다.</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>11.8</v>
+        <v>26.2</v>
       </c>
       <c r="F2" t="n">
-        <v>776</v>
+        <v>1488</v>
       </c>
       <c r="G2" t="n">
-        <v>65.77</v>
+        <v>56.8</v>
       </c>
       <c r="H2" t="n">
         <v>6.11</v>
@@ -511,48 +517,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2회차</t>
+          <t>1회차</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>아 더빙.. 진짜 짜증나네요 목소리</t>
+          <t>너무재밓었다그래서보는것을추천한다</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>## [VOC 데이터 분석 보고]
-**✅ 민원 요약 (1줄)**
-콘텐츠 내 더빙 목소리의 음질 또는 연기 퀄리티에 대해 고객이 강한 불만과 불쾌감을 표출함.
----
-**🔍 VOC 분석 및 가이드**
-**1. 카테고리 분류:**
-*   **주요 카테고리:** 콘텐츠/제품 품질 (Audio/Voice Quality)
-*   **키워드:** 더빙, 목소리, 불쾌감, 짜증 (Aesthetic/Functional dissatisfaction)
-*   **감성 지표:** 매우 부정적 (High Negativity)
-**2. 잠재적 원인 분석 (Root Cause Hypothesis):**
-*   **음향 기술적 결함:** 마이크 노이즈, 배경 잡음(Static), 부자연스러운 음향 처리, 대사 전달력 부족 등
-*   **연기 퀄리티 문제:** 캐릭터 설정과 맞지 않는 톤, 과도하거나 기분 나쁜 발성, 감정 전달의 부재 등
-*   **콘텐츠/기술적 오류:** 더빙 트랙과 영상/자막의 싱크(Sync) 불일치로 인한 부자연스러움.
-**3. 대응 가이드 (Action Plan):**
-| 단계 | 목표 | 세부 실행 방안 | 담당 부서 |
+          <t>## 🔍 사내 VOC 데이터 분석 보고
+**[분석 담당자: VOC 데이터 분석가]**
+**[분석 일시: 202X. XX. XX]**
+**[데이터 상태: 긍정적/추천형 (Positive/Advocacy)]**
+---
+### 📝 1. 1줄 요약 (One-Line Summary)
+해당 고객은 제품/서비스에 대해 **강한 만족도**를 표현하며 타인에게 적극적으로 **추천할 의향**이 있음을 강력하게 시사함.
+---
+### 📈 2. VOC 분석 및 대응 가이드 (Action Guide)
+#### 📊 분류 및 지표 (Classification &amp; Metrics)
+* **VOC 유형:** 긍정적 후기 (Praise / Recommendation)
+* **주요 키워드:** (추론됨) 만족, 재미, 추천
+* **분석 의의:** 해당 피드백은 매우 강력한 **NPS(순추천고) 지표**로 간주할 수 있으며, 현재 제공되는 경험의 핵심 강점(Key Strength)을 확인시켜 줌.
+#### 💡 핵심 인사이트 (Key Insights)
+1. **경험의 성공 입증:** 고객이 느끼는 '즐거움'이라는 감정적 요소가 서비스 또는 제품의 핵심 가치로 성공적으로 전달되었음을 의미함.
+2. **바이럴 마케팅 자원 확보:** 이 피드백은 향후 마케팅 자료(Testimonial, 광고 카피 등)로 즉시 활용 가능한 '진짜 고객 목소리'입니다.
+3. **일관성 검토의 필요성:** 현재 긍정적 경험을 준 특정 접점(Touchpoint)이 무엇인지 파악하여, 모든 고객에게 이와 같은 수준의 경험을 제공할 수 있도록 프로세스 일관성을 검토해야 합니다.
+#### 🚀 실행 권고 사항 (Recommended Action Plan)
+| 구분 | 실행 방안 | 담당 부서 | 목표 (Goal) |
 | :--- | :--- | :--- | :--- |
-| **단기 (Immediate)** | 고객 불만 경청 및 정보 확보 | 1) **공감 및 사과:** 감정적 만족도가 높으므로 적극적인 공감을 통해 사안의 심각성을 인정함. 2) **구체적 정보 요청:** 어떤 콘텐츠(게임, 영상 등), 어떤 캐릭터의 목소리인지 구체적인 정보(버전, 시점)를 재요청하여 이슈의 범위를 좁힘. | CS팀 / 운영팀 |
-| **중기 (Medium-Term)** | 문제의 근본 원인 파악 및 개선 | 1) **사운드 QA 재검토:** 해당 콘텐츠의 더빙 녹음 파일과 최종 마스터링 단계의 음향을 기술팀이 재검토하여 객관적 품질 문제를 확인. 2) **더빙 가이드 재정립:** 연기 디렉션 가이드(톤, 발음, 감정선)가 현장 녹음진에게 명확히 전달되었는지 확인하고, 부족할 경우 가이드 강화. | 제작/PD팀 / 사운드 디자인팀 |
-| **장기 (Long-Term)** | VOC 기반 품질 관리 시스템 정착 | 1) **사전 검수 프로세스 강화:** 최종 배포 전 '목소리 품질 검수 체크리스트(Voice Quality Checklist)'를 마련하고, 음향 전문가의 검수 단계를 의무화함. 2) **작품별 톤 앤 매너 표준화:** 캐릭터 성격에 따른 적절한 음성 레퍼런스를 DB화하여 향후 제작 시 품질 편차를 최소화. | 기획/QA팀 |</t>
+| **단기 대응** | 고객에게 감사 메시지를 전달하고, 해당 경험의 이유(칭찬받은 부분)를 구체적으로 재확인하는 후속 조치(Follow-up) 실시. | 고객지원팀 (CS) | 고객 로열티(Loyalty) 강화 및 관계 구축 |
+| **중기 대응** | 해당 고객에게 공식적인 리뷰 작성 또는 영상 후기 작성을 정중하게 요청함. | 마케팅팀 (Marketing) | 검증된 긍정적 바이럴 콘텐츠 확보 |
+| **장기 대응** | 성공 경험을 유발한 내부 요소(UI, 콘텐츠, 프로세스 등)를 식별하여, 제품/서비스의 표준 운영 절차(SOP)에 반영하고 강화함. | 기획팀/제품팀 (Product) | 긍정적인 경험의 재현성(Repeatability) 확보 |</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>14.81</v>
+        <v>15.08</v>
       </c>
       <c r="F3" t="n">
-        <v>1278</v>
+        <v>1331</v>
       </c>
       <c r="G3" t="n">
-        <v>86.28</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="H3" t="n">
         <v>6.11</v>
@@ -561,45 +571,44 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3회차</t>
+          <t>1회차</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>아 더빙.. 진짜 짜증나네요 목소리</t>
+          <t>교도소 이야기구먼 ..솔직히 재미는 없다..평점 조정</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>## 📊 사내 VOC 분석 보고서
-**[분석 대상]** 고객 민원 (The Voice of Customer)
-**[분석자]** VOC 데이터 분석팀
----
-### 📝 1. 핵심 요약 (Key Summary)
-**더빙(Dubbing) 목소리의 품질 및 표현 방식에 대해 고객이 강한 불만(짜증)을 표출함.**
----
-### 💡 2. 대응 가이드 (Action Guideline &amp; Analysis)
-**📌 [분석 관점]**
-본 민원은 특정 콘텐츠(또는 제품)의 **오디오 품질(Audio Quality)** 또는 **보이스 캐스팅(Voice Casting)**에 대한 주관적인 만족도 저하를 나타냅니다. 단순한 불평이 아니라, 몰입도를 저해하는 명확한 **UX(User Experience) 문제**로 간주하고 대응해야 합니다.
-**✅ [즉각 조치 (Immediate Action)]**
-1. **로그 분류 및 우선순위 지정:** 해당 민원을 '콘텐츠/미디어 품질 이슈'로 즉시 분류하고, 심각도 '중(Medium) 이상'으로 설정하여 **콘텐츠 제작팀 또는 음향 기술팀**에 에스컬레이션합니다.
-2. **추가 정보 확보 요청:** 담당자에게 해당 콘텐츠의 세부 정보(제목, 버전, 플레이 시간 등)와 가능하다면 **'어떤 부분이 짜증나는지'** (예: 목소리 톤이 부자연스럽다, 발음이 불분명하다, 감정 전달이 안 된다 등)에 대한 추가 피드백을 요청하여 문제의 원인을 구체화해야 합니다.
-**🛠️ [심층 개선 (Deep Dive Improvement)]**
-1. **벤치마킹 검토:** 경쟁사 혹은 타 제품의 더빙/음성 연기 수준을 벤치마킹하여 자사의 오디오 기준이 업계 표준에 미치는지 내부 점검이 필요합니다.
-2. **QA 체크리스트 보완:** 콘텐츠 배포 전, '음성 품질 체크리스트' 항목에 '톤의 적절성', '감정의 일관성', '명료성' 등을 필수적으로 포함하도록 QA 프로세스를 보완해야 합니다.</t>
+          <t>## 📝 VOC 분석 보고서
+### 📌 1줄 요약 (Summary)
+콘텐츠(또는 서비스)의 재미 요소가 결여되었다는 불만을 제기하며, 현재의 평점 시스템 또는 콘텐츠 질적 수준에 대한 전반적인 조정 및 개선을 요구함.
+---
+### 💡 분석 가이드 및 향후 조치 (Guideline &amp; Action Plan)
+해당 민원은 단순한 불만을 넘어 **콘텐츠 경험(UX)** 및 **운영 시스템(Rating System)**에 대한 근본적인 피드백이므로, 아래의 절차에 따라 다각도로 검토가 필요합니다.
+**1. [🔍 Fact Check &amp; 원인 분석]**
+*   **대상 특정:** 민원 내용만으로는 해당 콘텐츠나 서비스의 주제를 정확히 파악할 수 없으므로, 추가적인 맥락(어떤 프로그램, 메뉴, 자료 등)을 확인해야 합니다.
+*   **Pain Point 도출:** 사용자에게 '재미가 없다'고 판단되는 구체적인 지점이 무엇인지 (예: 내용의 진부함, 몰입도 저하, 전달 방식의 지루함)를 분석하여 정성적 원인을 파악해야 합니다.
+**2. [🛠 시스템 검토 (Rating System)]**
+*   **현행 평점 시스템 점검:** 현재 콘텐츠 성격(교육용, 오락용, 정보 전달용 등)에 비해 평점 조정 요구가 과도하거나 시스템 자체가 사용자 만족도를 제대로 반영하지 못하고 있는지 확인해야 합니다.
+*   **시스템 개선 가능성 타진:** 단순 점수 조정 외에, 사용자가 콘텐츠의 가치를 더 명확히 인식할 수 있도록 평점 기준(예: 난이도, 흥미도, 전문성 등)을 세분화하는 방안을 검토합니다.
+**3. [🚀 후속 조치 및 제언]**
+*   **Content Improvement 요청:** 만약 해당 콘텐츠가 사내 필수 시청/이용 자료라면, 재미 요소를 가미하거나 구성 방식을 변경하는 방향으로 콘텐츠 담당 부서에 개선을 요청해야 합니다.
+*   **VOC 피드백 루프 구축:** 이러한 '경험 부족' 민원이 반복될 경우, 해당 서비스의 재설계(Redesign)가 필요할 수 있으므로, 유사 민원 발생 시 우선적으로 상위 레벨의 서비스 평가를 진행할 것을 제언합니다.</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>10.83</v>
+        <v>10.64</v>
       </c>
       <c r="F4" t="n">
-        <v>955</v>
+        <v>940</v>
       </c>
       <c r="G4" t="n">
-        <v>88.17</v>
+        <v>88.36</v>
       </c>
       <c r="H4" t="n">
         <v>6.11</v>
@@ -608,44 +617,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4회차</t>
+          <t>1회차</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>아 더빙.. 진짜 짜증나네요 목소리</t>
+          <t>막 걸음마 뗀 3세부터 초등학교 1학년생인 8살용영화.ㅋㅋㅋ...별반개도 아까움.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>## 📢 VOC 데이터 분석 보고서
-**분석자:** 사내 VOC 데이터 분석가
----
-### 🎤 1줄 요약 (Summary)
-사용자는 서비스 내 콘텐츠 더빙의 목소리 품질 및 표현 방식에 대해 **강한 불만(높은 불쾌감)**을 표하며, 음성 콘텐츠의 개선을 요구하고 있음.
----
-### 🔍 대응 가이드 (Action Guide)
-| 분류 | 내용 | 비고 |
-| :--- | :--- | :--- |
-| **핵심 이슈** | 콘텐츠 음향 품질(더빙/성우 목소리) | 콘텐츠 제작/운영팀 담당 |
-| **감성 분석** | 부정 (Negative) / 불쾌감 표출 (Frustrated) | 즉각적인 대응 필요 |
-| **긴급도** | 중~상 (High) | 불만 강도가 높으므로 즉시 추적 필요 |
-| **분석 가이드** | **[1단계: 데이터 확장]** 해당 민원이 특정 콘텐츠(게임, 영상, 이벤트 등)에 국한된 것인지, 아니면 서비스 전체의 보편적인 문제인지 추가 VOC 및 로그를 통해 파악해야 함. | |
-| **조치 가이드** | **[2단계: 원인 규명]** 해당 콘텐츠의 오디오 소스(더빙)가 원본 스크립트와 일치하는지, 사용자가 느끼는 '짜증'이 발성/톤의 문제인지, 기술적인 음질(압축, 노이즈)의 문제인지 관련 제작팀과 협업하여 구체적인 피드백을 수집해야 함. | |
-| **제안 사항** | **[3단계: 개선안 제시]** 제작팀에 해당 피드백을 전달하고, 필요시 성우 재녹음 또는 음향 믹싱(믹싱/EQ 조정)을 검토하는 개선안을 제시하도록 팔로우업 필요. | 재작업(Re-do) 리스크 고려 |</t>
+          <t>안녕하십니까. 사내 VOC 데이터 분석가로서 해당 민원에 대한 핵심 요약 및 후속 대응 가이드를 보고 드립니다.
+---
+## 📋 VOC 분석 리포트
+### 🟢 1. 민원 1줄 요약 (Key Insight)
+**특정 아동 대상 콘텐츠(3~8세)의 제작 품질 및 내용적 가치에 대한 고객의 불만이 높으며, 기대치에 미치지 못하는 콘텐츠에 대한 투자 대비 만족도(Value)가 매우 낮음을 지적하고 있습니다.**
+### 🟡 2. 심층 VOC 분석 (Deep Dive Analysis)
+*   **핵심 감정 (Sentiment):** 강한 실망 및 회의론 (Disappointment &amp; Skepticism).
+*   **핵심 키워드 (Keywords):** 3세, 8세, 초등 1학년, 아까움 (Waste/Disappointment).
+*   **VOC 유형:** 콘텐츠 품질 및 타겟 적절성(Content Quality &amp; Target Appropriateness).
+*   **분석 내용:** 이 민원은 단순히 영화 자체의 재미 여부를 떠나, **"이 연령대(3~8세)의 시청자가 기대하는 수준의 몰입도나 교육적 깊이가 해당 콘텐츠에 담겨 있지 않다"**는 평가를 내리고 있습니다. 고객은 이 콘텐츠를 '낭비'로 인식하고 있으며, 이는 콘텐츠의 차별성 또는 품질 관리 부문에서 개선이 필요함을 의미합니다.
+### 🟣 3. 후속 대응 가이드 (Actionable Guide)
+이 VOC를 단순한 불만으로 치부하지 말고, **'콘텐츠 품질의 재검토 요청'**으로 분류하여 담당 부서에 전달해야 합니다.
+**[A. 즉각적인 조치 (Short-Term Action)]**
+1.  **데이터 수집 및 검증:** 3~8세 타겟 콘텐츠의 평점, 리뷰 수, 경쟁사 콘텐츠의 평점 등을 비교하여 해당 콘텐츠가 시장 평균 대비 품질 측면에서 어느 지점에 위치하는지 객관적 수치로 검증합니다.
+2.  **피드백 회수:** 해당 민원 접수 채널을 통해 유사한 연령층(유아~초등 저학년)의 타 콘텐츠에 대한 불만이나 기대치를 추가로 수집합니다.
+**[B. 근본적인 개선 방안 (Long-Term Solution)]**
+1.  **콘텐츠 표준 재정립:** 3~8세라는 넓은 타겟 연령에 맞는 콘텐츠의 **최소 품질 기준(Minimum Viable Quality)**을 내부적으로 재정립해야 합니다. 연령별 발달 특성(예: 3세는 인지적 반복, 8세는 복잡한 스토리라인)을 고려한 세분화된 가이드라인이 필요합니다.
+2.  **평가 시스템 강화 (QA):** 콘텐츠 출시 전, 해당 연령대의 **실제 시청자 또는 전문가 그룹(Focus Group)**을 통해 콘텐츠의 몰입도, 교육적/정서적 가치, 시각적 만족도를 철저히 검증하는 QA(Quality Assurance) 단계를 의무화해야 합니다.
+3.  **가치 제안 강화 (Value Proposition):** 만약 콘텐츠 자체의 개선이 어렵다면, 해당 연령대 시청자에게 **"이 콘텐츠가 제공하는 독창적인 가치(재미, 학습, 공감 등)"**를 마케팅 측면에서 명확히 전달하여 고객이 느끼는 기대치와 실제 경험 사이의 괴리(Mismatch)를 줄여야 합니다.
+---
+**결론:** 해당 민원은 콘텐츠의 **'양'의 문제가 아닌 '질'의 문제**로 접근해야 하며, 아동 콘텐츠 제작 프로세스 전반에 걸친 품질 기준 강화가 시급해 보입니다.</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>12.24</v>
+        <v>17.32</v>
       </c>
       <c r="F5" t="n">
-        <v>1070</v>
+        <v>1498</v>
       </c>
       <c r="G5" t="n">
-        <v>87.43000000000001</v>
+        <v>86.48</v>
       </c>
       <c r="H5" t="n">
         <v>6.11</v>
@@ -654,47 +669,2322 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>1회차</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>원작의 긴장감을 제대로 살려내지못했다.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>## 🔎 사내 VOC 분석 리포트 (작성자: 데이터 분석팀)
+제시해주신 민원은 **콘텐츠의 핵심 가치(원작의 분위기 및 톤앤매너)**가 재가공되는 과정에서 손실되었다는 지적입니다. 이를 바탕으로 요약 및 대응 가이드를 제시합니다.
+---
+### 📝 1. 핵심 요약 (1줄 요약)
+원작이 가진 **극적 긴장감(Tension)**과 몰입감이 현재 제작/구현 과정에서 충분히 반영되거나 전달되지 못하고 있다는 원작 팬들의 아쉬움 및 불만 표출임.
+### 🛠️ 2. 전략적 가이드 (Actionable Guidance)
+**📌 분석 코멘트:** 이 민원은 단순한 '취향 차이'가 아니라, **'원작 충실도(Fidelity)'**와 **'연출적 완성도'**라는 두 가지 중요한 영역에서 기대치 미달이 발생했음을 시사합니다. 즉, '느낌'이나 '분위기'와 같은 비(非)정량적 요소를 설계 단계에서 놓쳤을 가능성이 높습니다.
+**✅ [실행 방안] 긴장감 회복을 위한 3단계 점검 프로세스 제안**
+**1단계: [원작 분석 및 정의] 가이드라인 재정립 (Discovery)**
+*   **조치 목표:** '원작의 긴장감'이 구체적으로 무엇을 의미하는지 객관적으로 정의합니다.
+*   **세부 실행:** 원작의 대사, 서사적 구조, 시각적 연출(색감, 편집 리듬 등) 중 어떤 요소가 긴장감을 조성했는지 전문가(작품 기획자, 원작 애호가)를 통해 역추적하고, 이를 **'긴장감 체크리스트(Tension Checklist)'** 형태로 문서화해야 합니다.
+**2단계: [중간 검수 및 피드백 루프] 주기적인 감성 검증 (Monitoring)**
+*   **조치 목표:** 제작 단계에서 긴장감이 해소되거나 이완되는 구간이 없는지 사전에 포착합니다.
+*   **세부 실행:** 대본 집필, 컨셉 아트, 초기 프리뷰 등 핵심 분기점마다 **'긴장감 척도(Tension Meter)'**를 설정하고, 정량적인 피드백뿐만 아니라 원작에 대한 깊은 이해를 가진 **'가이드 리뷰 팀'**을 통해 감성적 점검을 받도록 프로세스를 도입해야 합니다.
+**3단계: [최종 연출 검토] 톤앤매너 최종 확인 (Final Check)**
+*   **조치 목표:** 제작 완료 단계에서 분위기 왜곡이 발생하지 않도록 최종적으로 검토합니다.
+*   **세부 실행:** 최종 편집 전, 원작의 핵심적인 **'리듬(Pacing)'**을 유지했는지, 특정 장르적 클리셰에 매몰되어 원작의 특유의 톤이 훼손되지는 않았는지를 재점검하는 과정을 필수로 포함해야 합니다.
+---
+**💡 결론:** 이 민원은 제작 파이프라인 내 **'감성적 품질 관리(Emotional Quality Control)'** 시스템이 부재했음을 알려주는 중요한 신호로 해석하고, 단순한 피드백 처리가 아닌 **프로세스 개선의 계기**로 활용하시길 권고드립니다.</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1317</v>
+      </c>
+      <c r="G6" t="n">
+        <v>86.89</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1회차</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>별 반개도 아깝다 욕나온다 이응경 길용우 연기생활이몇년인지..정말 발로해도 그것보단 낫겟다 납치.감금만반복반복..이드라마는 가족도없다 연기못하는사람만모엿네</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>## 📢 VOC 분석 보고서
+**🔍 분석가 역할:** 사내 VOC 데이터 분석가
+**📋 민원 유형:** 콘텐츠 품질 및 연기력에 대한 극단적 비판 (Highly Negative / Content Critique)
+**📌 핵심 키워드:** 연기력 불만, 플롯 반복(납치/감금), 캐릭터 깊이 결여, 부정적 평가
+---
+### 📄 1줄 요약 (One-Line Summary)
+드라마의 연출 및 배우들의 연기력에 대해 극도의 불만과 부정적 평가를 표명하며 콘텐츠 완성도에 대한 강한 불쾌감을 표현함.
+---
+### 📋 데이터 분석 및 대응 가이드 (Action Guide)
+#### 1. 내부 분류 및 중요도 판단
+*   **분류:** 콘텐츠 피드백 (Content Critique) / 연출 및 캐스팅 관련 불만
+*   **감성:** 극도로 부정적 (Extremely Negative)
+*   **중요도:** ★★★☆☆ (양은 적으나, 충성도 있는 시청자의 강한 불만을 나타내므로 경시해서는 안 됨)
+#### 2. 핵심 이슈 추출 및 분석
+*   **주요 불만 지점:**
+    1.  **배우 연기력:** 특정 배우들의 연기 수준에 대한 근본적인 불만 및 비난이 주를 이룸.
+    2.  **플롯 및 구성:** 극의 전개가 반복적이고 단순하며, 캐릭터(가족 등)의 입체성이 부족하다고 평가함.
+    3.  **전체 몰입도:** 낮은 연기력과 반복적인 플롯이 시청 몰입도를 심각하게 저해하고 있음.
+*   **분석 요약:** 해당 민원은 서비스 운영상의 오류보다는, **콘텐츠 자체의 연출, 대본, 그리고 캐스팅에 대한 근본적인 시청자의 불만**을 반영하고 있습니다.
+#### 3. VOC 대응 전략 (Response Strategy)
+*   **[최우선 원칙] 감정적 비난에 절대 동요하지 말 것.** (개인적인 욕설이나 비속어에 반응하거나 감정적으로 대응하는 것은 피해야 합니다.)
+*   **[접근 태도] 공감 및 경청 (Acknowledge &amp; Listen).** 시청자의 매우 격렬한 의견임을 인지하고, 이 피드백이 다음 콘텐츠 제작에 반영될 수 있음을 전달하는 것에 초점을 맞춥니다.
+*   **[응대 방향]**
+    *   "시청자님께서 느끼시는 드라마의 연기와 구성에 대한 솔직하고 강한 의견을 접했습니다." 와 같이 **피드백 자체를 수용**하는 방향으로 응대합니다.
+    *   개인의 연기력에 대한 비방에는 직접 반박하기보다는, "시청자님의 이러한 솔직한 의견은 제작진이 작품의 완성도를 높이는 데 중요한 자료가 될 것입니다."라고 마무리하며 **피드백의 가치를 인정**해 주는 것이 가장 효과적입니다.
+*   **[내부 후속 조치]** 해당 피드백은 단순한 감정 해소용 답변으로 끝낼 것이 아니라, **콘텐츠 제작팀(연출팀/작가/Casting 담당)**에게 전달되어 향후 피드백 반영 시 시청자가 지적한 '캐릭터의 입체성'이나 '플롯의 진부함' 등의 요소를 점검하는 근거로 활용되어야 합니다.</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1541</v>
+      </c>
+      <c r="G7" t="n">
+        <v>87.70999999999999</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1회차</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>울면서 손들고 횡단보도 건널때 뛰쳐나올뻔 이범수 연기 드럽게못해</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>## 🔎 VOC 분석 결과 및 대응 가이드
+**[분석 관점]** 본 민원은 서비스/제품 자체의 결함이 아닌, **외부 콘텐츠(배우의 연기)에 대한 시청자/시청자의 개인적인 감상평 및 비평**에 해당합니다. 따라서 서비스 개선 차원의 즉각적인 내부 조치보다는 데이터 분류 및 공손한 피드백 관리 전략이 필요합니다.
+---
+### 📝 1줄 요약 (Complaint Summary)
+배우 이범수의 연기(특히 횡단보도 장면에서의 감정 표현)가 비현실적이며 몰입을 방해한다는 부정적 비평을 제기함.
+---
+### 📈 대응 가이드 (Action Plan)
+| 구분 | 내용 | 비고 |
+| :--- | :--- | :--- |
+| **1. 분류 (Category)** | **[콘텐츠 피드백 / 배우 평가]** | 내부 서비스 품질 이슈가 아님을 인지. |
+| **2. 대응 방향 (Stance)** | **경청 및 존중 (Listen &amp; Acknowledge)** | 제작진의 의도나 작품 자체의 완성도를 부정하기보다는 시청자의 감상을 존중하는 태도를 취함. |
+| **3. 내부 조치 (Internal Action)** | **데이터 수집 및 모니터링** | 해당 키워드(이범수, 연기, 횡단보도 등)를 중심으로 유사 민원 발생 추이를 추적하여, 연기력에 대한 전반적인 시청자 반응의 *추세*를 파악함. (단, 개별 민원에 대한 직접적 피드백은 불필요) |
+| **4. 고객 응대 가이드 (Customer Response)** | **[공개/비공개 응대 시]** | "시청자님의 솔직한 감상에 감사드립니다. 작품을 보시는 과정에서 몰입에 영향을 주는 요소가 있었던 것 같습니다. 의견을 전달해 주셔서 참고하겠습니다." 와 같이 감상 자체를 인정하며 종결함. (특정 배우의 연기 개선을 약속하는 것은 절대 금물) |</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1113</v>
+      </c>
+      <c r="G8" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1회차</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>취향은 존중한다지만 진짜 내생에 극장에서 본 영화중 가장 노잼 노감동임 스토리도 어거지고 감동도 어거지</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>## 🎬 VOC 데이터 분석 결과 보고
+**분석자:** [사내 VOC 데이터 분석가]
+**분석일:** 202X. XX. XX
+---
+### 📌 1줄 요약 (VOC Tag / Key Insight)
+**[콘텐츠 품질 불만]** 영화의 서사 구성(Story)과 정서적 몰입도(Emotional Impact)가 현저히 낮아 관람 만족도가 매우 낮음.
+---
+### 📝 심층 분석 및 가이드
+본 민원은 **‘콘텐츠의 품질 및 경험 부족’**에 대한 직접적인 불만으로, 단순히 서비스(상영 환경 등) 문제가 아닌 핵심 상품인 **‘영화 자체’**에 대한 부정적 피드백입니다.
+#### 🔍 1. 핵심 불만 사항 (Pain Points) 분석
+| 분석 항목 | VOC 내용 | 내포된 문제점 |
+| :--- | :--- | :--- |
+| **몰입도 저하** | "가장 노잼" | 콘텐츠의 재미(Fun Factor), 페이싱(Pacing) 등 기본적인 관람 재미 요소 부족. |
+| **내러티브 결함** | "스토리도 어거짐" | 이야기의 개연성(Plausibility)이나 서사 구조(Structure)가 불분명하거나 약함. |
+| **감정 이입 부족** | "감동도 어거지" | 관객의 감정을 건드리는 극적 장치, 연출력, 캐릭터 구축 등에 실패. |
+#### 📊 2. VOC 분류 및 중요도
+*   **VOC 분류:** 콘텐츠 만족도 (Content Satisfaction) / 관람 경험 저하 (Negative Experience)
+*   **심각도:** **높음 (High)**. 이는 단순한 불만이 아닌, 영화 선택 단계에서의 실망감과 콘텐츠 자체에 대한 거부감을 나타내기 때문입니다.
+#### 🚀 3. 데이터 분석가 관점의 가이드 및 후속 조치 제안
+**A. 단기적 대응 (Immediate Action):**
+1.  **피드백 기록 및 분류:** 해당 민원을 '내러티브 약함' 또는 '감동 부족' 태그로 시스템에 즉시 분류하여 콘텐츠 성향 데이터를 축적합니다.
+2.  **선별적 응대:** 고객에게 "제시해주신 스토리 및 감동 관련 피드백은 콘텐츠 기획 측에 전달하여 반영하도록 노력하겠습니다"라는 형태로, 고객의 의견을 경청했음을 알리고 경험 저하에 대한 유감 표명(Apology)을 전달합니다.
+**B. 중장기적 개선 방향 (Strategic Action):**
+1.  **콘텐츠 퀄리티 QC 강화 (Distributor/Platform 관점):**
+    *   상영작 또는 추천작 선정 시, 단순 흥행 지표 외에 '스토리 완성도', '평론가 평점 분포', '관람 만족도(재관람 의사 등)'와 같은 **질적 지표(Qualitative Metrics)**를 추가로 검토하는 QC 프로세스를 구축해야 합니다.
+2.  **관객 페르소나 재정의 (Marketing 관점):**
+    *   만약 해당 영화가 타 타겟층을 위한 것이었다면, 광고 및 마케팅 메시지가 영화의 실제 품질(노잼, 노감동)을 정확하게 반영하고 있는지 점검해야 합니다. 기대치를 과도하게 높이는 홍보가 불만으로 이어질 수 있습니다.
+3.  **메타데이터 활용 증대:**
+    *   이러한 '서사', '몰입도' 관련 키워드를 긍정/부정 감성 분석(Sentiment Analysis) 결과에 반영하여, 어떤 장르나 감독의 작품이 지속적으로 관객의 '감정 이입'을 방해하는지 데이터화해야 합니다.</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1404</v>
+      </c>
+      <c r="G9" t="n">
+        <v>88.03</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1회차</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>굿바이 레닌 표절인것은 이해하는데 왜 뒤로 갈수록 재미없어지냐</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>## [사내 VOC 데이터 분석 보고]
+**분석 담당:** OOO (사내 VOC 데이터 분석가)
+**민원 분류:** 콘텐츠 만족도 저하 (Content Engagement Drop)
+---
+### 💡 1줄 요약 (VOC Summary)
+작품의 초기 설정(표절 요소)은 수용 가능하나, 전개 후반부로 갈수록 서사의 밀도와 몰입도가 현저히 떨어져 중도 이탈을 유발하는 콘텐츠 피로도에 대한 불만이 제기됨.
+---
+### 🧭 가이드 및 후속 조치 제안 (Actionable Guide)
+해당 민원은 단순한 비판을 넘어 **'서사적 지속 가능성(Sustained Narrative Potential)'**에 대한 근본적인 의문을 제기하고 있으므로, 콘텐츠 기획 단계에서 다음의 세 가지 관점을 재검토해야 합니다.
+#### 📌 **1. 서사 구조 및 페이싱(Pacing) 검토 (Immediate Focus)**
+*   **문제 진단:** 후반부 전개에서 몰입도가 떨어진다는 것은 주요 갈등 해소 지점(Climax)이 지연되거나, 새로운 위협 요소의 등장 속도가 느려지고 있음을 의미합니다.
+*   **액션 아이템:** 콘텐츠의 전체 러닝타임 대비 각 에피소드/파트별 '흥미 지표(Interest Spike)'를 시각화하고, 특정 지점(예: 50% 이상 시점)에서 서사적 긴장감이 급격히 약해지는 구간이 있는지 점검해야 합니다.
+#### 📌 **2. 콘텐츠의 '신선도' 유지 전략 (Mid-Term Strategy)**
+*   **문제 진단:** 표절이라는 선을 인지한 시청자들은 새로운 '변주'나 '심화된 해석'을 요구합니다. 반복되는 패턴은 즉각적인 흥미 상실로 이어집니다.
+*   **액션 아이템:** 초반 설정(표절 기반의 세계관)을 **활용**하되, 그것을 벗어나는 **새로운 변수(Twist)** 또는 캐릭터의 내적 성장을 주입하여 시청자에게 '재미' 외의 '지적/감정적 보상'을 제공해야 합니다.
+#### 📌 **3. 타겟 유저 이탈 지점 분석 (Data Driven Insight)**
+*   **문제 진단:** 정성적 민원이지만, 실제 데이터를 통해 이탈률이 급증하는 지점(Drop-off point)이 있다면 이는 가설을 증명하는 중요한 데이터가 됩니다.
+*   **액션 아이템:** 유저 로그 데이터를 기반으로 '이탈률이 가장 높은 시청 구간'을 정확히 파악하고, 해당 구간 직전과 직후에 어떤 내용(정보량, 액션 강도, 캐릭터 비중 등)이 배치되었는지 분석하여 피드백을 해당 팀에 전달해야 합니다.</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1287</v>
+      </c>
+      <c r="G10" t="n">
+        <v>87.66</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1회차</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>재미없다 지루하고. 같은 음식 영화인데도 바베트의 만찬하고 넘 차이남....바베트의 만찬은 이야기도 있고 음식 보는재미도 있는데 ; 이건 볼게없다 음식도 별로 안나오고, 핀란드 풍경이라도 구경할랫는데 그것도 별로 안나옴 ㅡㅡ</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>## 🔍 VOC 분석 결과 및 대응 가이드
+### 📄 1줄 요약 (Summary)
+**경쟁작(바베트의 만찬 등) 대비 콘텐츠의 몰입도와 깊이가 현저히 떨어진다는 불만이며, 주요 시청 포인트인 스토리, 음식의 시각적 매력, 그리고 배경(풍경) 활용의 부재로 인해 극심한 지루함을 호소함.**
+---
+### 🛠️ 대응 가이드 (Actionable Strategy)
+본 민원은 단순한 '재미없다'는 감상평이 아니라, **기존 경쟁 제품(바베트의 만찬)과의 핵심 요소(콘텐츠 밀도, 시각적 경험) 비교를 통한 명확한 '기능적 결함' 지적**입니다. 다음과 같은 관점에서 개선 기획을 제안합니다.
+#### 1. 콘텐츠 및 스토리 구조 개선 (Pacing &amp; Narrative)
+*   **[개선 필요] 지루함 해소:** 현재 콘텐츠가 서사가 단편적이거나 느리다는 지적이 있습니다. 주요 장면 사이의 공백을 채우거나, 등장인물의 동기/갈등을 구체화하여 관객이 '볼 것'이 없다는 인상을 해소해야 합니다.
+*   **[벤치마킹] 경쟁작 분석:** '바베트의 만찬'이 가진 강점(이야기 흐름, 인물의 감정선 등)을 분석하여, 우리 제품에 어떤 스토리 구조를 이식할 수 있을지 검토해야 합니다.
+#### 2. 시각적 만족도 극대화 (Visual Appeal - Food &amp; Setting)
+*   **[개선 필요] 음식의 '경험' 디자인:** 음식이 단순히 '나오는 것'이 아니라, 그 음식을 통해 어떤 감정(만족감, 갈등, 역사 등)이 표현되는지 연출이 필요합니다. 밋밋한 플레이팅이나 클로즈업만으로는 시선을 사로잡기 어렵습니다.
+*   **[활용 강화] 배경(핀란드 풍경)의 서사적 기능 부여:** 배경을 단순히 '장소'로 남기지 말고, 핀란드 풍경 자체가 캐릭터의 감정 변화나 사건의 전개에 영향을 미치는 장치(Setting Device)로 활용되어야 합니다. (예: 고독한 핀란드 풍경 속 인물의 고뇌, 변화하는 계절의 음식 등)
+#### 3. VOC 후속 조치 제안
+*   **제품 차원:** 스토리라인 및 미장센(음식/풍경 연출)의 개선을 최우선 과제로 반영하고, 개선 완료 시 로드맵을 고객에게 안내할 필요가 있습니다.
+*   **단기 대응:** 고객이 기대했던 '시각적 재미'가 부족하다는 점을 인정하고, 향후 제작 방향이나 추가적인 콘텐츠/기능에 대한 로드맵을 제시하며 기대감을 재정립하는 응대가 효과적일 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1312</v>
+      </c>
+      <c r="G11" t="n">
+        <v>87.33</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2회차</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>아 더빙.. 진짜 짜증나네요 목소리</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>## [VOC 데이터 분석 보고서]
+**분석 담당:** 사내 VOC 데이터 분석가
+---
+### 📄 1. 민원 요약 (One-Line Summary)
+사용자들은 서비스 내 더빙(성우) 목소리의 톤이나 연기 퀄리티가 만족스럽지 못하며, 이에 대한 강한 거부감과 불만을 표현하고 있습니다.
+***
+### 🛠️ 2. 개선 가이드 (Action Guide)
+**▶ 담당 부서:** 콘텐츠 제작팀 / 로컬라이제이션(Localization)팀 / UX 기획팀
+**▶ 상황 진단:**
+단순한 '선호도 차이'일 수도 있으나, '짜증나다'는 감정 표현은 사용자 경험(UX)을 저해하는 중요한 요소입니다. 단순히 "싫어하는 사람"의 의견이 아니라, 서비스의 몰입도나 완성도를 저해하는 품질 문제로 간주하고 접근해야 합니다.
+**▶ 우선 수행 조치 (Immediate Actions):**
+1. **감성/세부 키워드 확장:** 해당 민원을 "음성 피로도", "화질/음질 저하", "캐릭터 불일치" 등 더 넓은 범위의 키워드로 분류하여, 동일한 불만이 다른 사용자에게도 확산되고 있는지 교차 분석해야 합니다. (단일 이슈인지, 광범위한 품질 문제인지 확인)
+2. **심층 분석 요청 (Context Gathering):** 사용자에게 구체적인 피드백을 요청할 필요가 있습니다. (예: "어떤 부분이 짜증나셨나요? 목소리의 톤인가요, 연기의 감정 표현인가요? 아니면 음질 문제인가요?")
+**▶ 중장기 개선 방안 (Strategic Solutions):**
+1. **품질 기준 재검토 (QC):** 현재 더빙 작업이 통과한 품질 기준(QC Checklist)을 재점검하고, 해당 기준이 사용자 경험(User Experience) 측면에서 충분한지 검증해야 합니다. (예: 목소리 톤의 변화, 발음의 명료도, 감정선의 일관성 점검)
+2. **선택권 제공 고려 (Feature Improvement):** 만약 더빙 목소리가 사용자에게 부정적 경험을 주고 있다면, 원어 음성 청취 옵션이나 '음성 설정 변경' 옵션을 제공하는 등의 선택권 도입을 UX 기획 차원에서 검토해야 합니다.
+3. **성우 리소스 변경 (Content Update):** 단편적인 문제라면, 해당 캐릭터나 콘텐츠에 투입되는 성우 리소스 및 연출 디렉팅을 변경하여 품질을 재검토하는 작업을 진행해야 합니다.</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1151</v>
+      </c>
+      <c r="G12" t="n">
+        <v>87.94</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2회차</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>너무재밓었다그래서보는것을추천한다</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>## 🔍 VOC 데이터 분석 결과
+**[민원 내용]**
+&gt; "너무재밓었다그래서보는것을추천한다"
+---
+### 📄 1줄 요약 (Summary)
+고객이 해당 서비스(또는 콘텐츠)에 대해 매우 높은 만족도를 표현하며, 주변에 적극적으로 추천할 의향이 있는 **'극강의 긍정 후기'**입니다. (불만 사항이 아닌 강력한 추천 데이터입니다.)
+### 📈 VOC 분석 및 대응 가이드 (Guideline)
+**1. 데이터 유형 분류:**
+*   **유형:** 강력한 추천(Advocacy), 긍정 피드백(Positive Feedback)
+*   **핵심 키워드:** 만족도 최상, 추천 의사 표명
+*   **분석 우선순위:** ⭐⭐⭐⭐⭐ (매우 높음)
+**2. 내부 액션 플랜 (Action Plan):**
+| 분류 | 실행 내용 | 세부 지침 | 기대 효과 |
+| :--- | :--- | :--- | :--- |
+| **감사 및 보상** | 즉각적인 감사 응대 | 긍정적 경험을 공유해 준 고객에게 감사 인사 전달 및 소정의 리워드(포인트, 쿠폰 등) 제공. | 로열티 강화 및 재방문 유도 |
+| **핵심 가치 추출** | 긍정 요소 맵핑 (Feature Mapping) | "너무재밌었다"가 구체적으로 어떤 기능/부분(ex. UI, 스토리, 성능)에서 만족을 얻었는지 추가 대화(Follow-up)를 통해 파악. | 제품 개선 및 마케팅 포인트 확정 |
+| **확산 전략** | 성공 사례 활용 (Testimonial) | 해당 후기를 익명 혹은 허가를 받아 공식 채널(SNS, 웹사이트 등)의 성공 사례로 활용 검토. | 바이럴 마케팅 효과 극대화 |
+**3. 담당자 코멘트:**
+해당 피드백은 **가장 가치 있는 마케팅 자원**입니다. 단순 응대로 끝내지 마시고, 이 강력한 만족의 이유(Why?)를 파고들어 다른 잠재 고객에게 확산될 수 있도록 구조화하는 것이 중요합니다.</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1119</v>
+      </c>
+      <c r="G13" t="n">
+        <v>88.86</v>
+      </c>
+      <c r="H13" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2회차</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>교도소 이야기구먼 ..솔직히 재미는 없다..평점 조정</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>## 📋 사내 VOC 데이터 분석 보고서
+**수신:** 콘텐츠 기획팀, 서비스 운영팀
+**참조:** CS 매니저
+**작성자:** VOC 데이터 분석팀
+**작성 일자:** YYYY.MM.DD
+---
+### 1. 💬 VOC 1줄 요약 (Key Takeaway)
+특정 테마(교도소)의 콘텐츠가 사용자에게 낮은 몰입도와 재미를 제공하고 있다는 불만이며, 이로 인해 서비스 평점 저하 및 만족도 하락에 대한 이의 제기(평점 조정 요구)로 분석됨.
+---
+### 2. 💡 VOC 분석 및 대응 가이드 (Action Plan)
+본 민원은 단순한 평점 불만이 아니라, **핵심 콘텐츠의 흥미 요소(Engagement)가 목표 사용자층의 기대를 충족시키지 못하고 있음**을 시사합니다. 즉, 콘텐츠의 **'퀄리티 이슈'**로 진단하고, 단기적 응대와 중장기적 개선을 병행해야 합니다.
+#### 🔍 1단계: 원인 분석 (Root Cause Analysis)
+*   **콘텐츠-사용자 매칭 오류:** '교도소 이야기'와 같은 극단적인 테마 자체가 특정 타깃에게는 흥미 유발 요소가 되지 못할 수 있습니다. 사용자 기대치와 실제 콘텐츠의 전달 방식 간의 괴리를 확인해야 합니다.
+*   **테마의 깊이 부족:** 단순히 사건을 나열하는 수준의 서술이라면, 사용자는 쉽게 '지루함(No Fun)'을 느낄 수 있습니다. 서사적 깊이, 캐릭터의 입체성, 극적 긴장감 등이 부족할 가능성이 높습니다.
+#### 🎯 2단계: 단기 대응 전략 (Immediate Action)
+1.  **민원 응대 (CS):**
+    *   **공감 우선:** 단순한 '재미'에 대해 부정하는 감정(솔직히 재미는 없다)에 대해 방어적인 태도를 보이지 않고, 사용자 경험에 대한 의견을 적극적으로 경청하며 공감합니다.
+    *   **데이터 요청:** "어떤 지점/특정 에피소드에서 흥미를 잃으셨는지" 등 구체적인 피드백을 요청하여 다음 콘텐츠 개선의 씨앗으로 활용합니다.
+2.  **내부 데이터 점검:**
+    *   **이탈 지점 확인:** 해당 테마의 콘텐츠를 소비한 사용자의 **재접률(Retention Rate)** 및 **중도 이탈 지점(Drop-off Point)** 데이터를 추출하여, 사용자가 어느 지점에서 흥미를 잃었는지 정량적으로 파악합니다.
+#### 📈 3단계: 중장기 개선 전략 (Long-term Improvement)
+**A. 콘텐츠 고도화 (Content Refinement)**
+*   **서사적 재구성:** 테마 자체가 아닌, '이야기'로서의 가치를 높여야 합니다. (Ex: 단순 사실 나열 → 인물 간의 심리 묘사, 극적 갈등 심화, 사건의 미스터리화 등)
+*   **사용자 피드백 반영 루프 구축:** VOC 분석팀에서 추출한 불만(재미 없음)을 기획팀에 전달할 때, 단순 민원으로 처리하지 않고 **'Critical Friction Point'**로 정의하여 반드시 콘텐츠 개선 우선순위에 올리도록 시스템화해야 합니다.
+**B. 포트폴리오 다각화 (Diversification)**
+*   **테마 확장 및 검증:** 현재 '교도소' 테마 외에 사용자들의 다양한 흥미를 유발할 수 있는 잠재적 테마(미스터리, 휴먼 드라마, 사회 비판 등)의 콘텐츠를 제작하고, 소규모 파일럿 테스트(A/B 테스트)를 통해 재미 지표를 사전에 검증해야 합니다.
+**[결론 및 제언]**
+이번 VOC는 콘텐츠의 '장르적 성공 여부'를 검토할 중요한 기회입니다. 해당 콘텐츠를 재검토하여 **'정보 전달'의 단계에서 '감성적 몰입'의 단계로 콘텐츠의 질을 끌어올리는 작업**이 필요합니다.</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>18.27</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1615</v>
+      </c>
+      <c r="G14" t="n">
+        <v>88.37</v>
+      </c>
+      <c r="H14" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2회차</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>막 걸음마 뗀 3세부터 초등학교 1학년생인 8살용영화.ㅋㅋㅋ...별반개도 아까움.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>## [VOC 데이터 분석 보고]
+### 📋 1줄 요약 (Summary)
+**타겟 연령대(3~8세)의 콘텐츠 적합성 및 완성도에 대한 불만 제기.** (광범위한 연령대를 아우르려다 기대치에 미치지 못하는 콘텐츠 품질에 실망함.)
+---
+### 💡 가이드 (Action &amp; Analysis Guide)
+**✅ 키워드 (Keywords):**
+콘텐츠 불만, 타겟 불일치, 연령별 적합성(Age Suitability), 품질 저하, 기대치 불일치(Expectation Gap)
+**📊 영향도 분석 (Impact Assessment):**
+*   **심각도:** 중하 (High Impact, Low Frequency)
+*   **핵심 이슈:** 특정 연령층을 명확히 분류하지 못하고 '대중적인' 콘텐츠를 만들려다, 특정 타겟에게는 지루하거나 불친절한 콘텐츠로 인식됨.
+*   **잠재 리스크:** 타겟팅 실패 시 재방문율 하락 및 부정적 리뷰 확산 위험.
+**🛠️ 실행 가이드 (Action Plan):**
+**1. [단기 조치] 콘텐츠 튜닝 및 검증 (Content Review):**
+*   해당 영화/콘텐츠의 **주요 연령대별 시청자 리뷰 및 선호도 데이터를 즉시 추출**하여, 3세 그룹과 8세 그룹의 핵심 불만 사항을 분류합니다.
+*   콘텐츠의 **'난이도 곡선(Difficulty Curve)'**을 진단하여, 모든 연령이 흥미를 느낄 수 있도록 명확한 **킬링 포인트(Hook) 설정**이 되어 있는지 점검합니다.
+**2. [중기 조치] 타겟 세분화 (Target Segmentation):**
+*   '3세~8세'와 같이 넓은 범위로 지정하기보다, **'Pre-K (3~5세)', 'Early Elementary (6~8세)'** 등 세분화된 타겟을 설정하고 각 그룹에 최적화된 콘텐츠를 기획하는 전략이 필요합니다.
+*   VOC 데이터를 기반으로 연령대별 **콘텐츠 페르소나**를 구축하고, 콘텐츠 개발 시 필수 검토 항목에 포함시킵니다.
+**3. [장기 조치] 개발 프로세스 개선 (Process Improvement):**
+*   콘텐츠 제작 초기 기획 단계에서 **'연령별 포커스 그룹 테스트(Focus Group Test)'**를 의무화합니다. 즉, 개발 완료 후 VOC가 발생하기 전에 다양한 타겟의 검증을 거치는 프로세스를 정착시켜야 합니다.</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>15.52</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1362</v>
+      </c>
+      <c r="G15" t="n">
+        <v>87.76000000000001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2회차</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>원작의 긴장감을 제대로 살려내지못했다.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>사내 VOC 데이터 분석가로서 해당 민원에 대한 요약 및 분석 가이드를 제출합니다.
+***
+### **[VOC 분석 보고서]**
+#### **1. 💬 민원 핵심 요약 (One-Line Summary)**
+원작이 가진 고유의 몰입감이나 극적 긴장감(서스펜스)이 구현 단계에서 희석되거나 누락되었다는 품질 저하 지적입니다.
+#### **2. 🔍 핵심 키워드 및 감성 분석**
+*   **핵심 키워드:** 긴장감, 원작 재현, 몰입도, 연출
+*   **감성:** 실망, 아쉬움, 불만 (Strong Negative)
+*   **분석 방향:** 감성적인 만족도 결여 지점으로, 표면적인 완성도보다 서사적/분위기적 충족도에 미흡하다는 피드백입니다.
+#### **3. 💡 개선 가이드 및 후속 조치 제안**
+**✅ [분석팀/기획팀 대상]:**
+1.  **원작 대조 검토 (Source Material Audit):** 원작의 주요 긴장감이 발생하거나 최고조에 달하는 지점을 특정하여 현재 결과물과 1:1 매칭되는 연출/전개 요소가 빠졌는지 검증해야 합니다. (예: 특정 복선 회수 시점, 감정적 충돌 지점 등)
+2.  **연출/속도감 재조정 (Pacing &amp; Execution):** 긴장감을 형성하는 '느린 전개(Slow Burn)'나 '정보의 단계적 노출' 등 서스펜스를 유지하는 핵심 기법이 의도적으로 생략되었는지 확인하고, 각 장면의 템포를 재조정하는 검토가 필요합니다.
+3.  **아티스트/팀 피드백 요청:** 제작진이 원작의 핵심 톤 앤 매너를 이해하고 구현했는지에 대한 정성적 피드백을 다시 요청하고, 부족한 부분을 보충할 수 있는 보충 시점(예: 후반부 연출 강화)을 설정해야 합니다.</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="F16" t="n">
+        <v>843</v>
+      </c>
+      <c r="G16" t="n">
+        <v>88</v>
+      </c>
+      <c r="H16" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2회차</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>별 반개도 아깝다 욕나온다 이응경 길용우 연기생활이몇년인지..정말 발로해도 그것보단 낫겟다 납치.감금만반복반복..이드라마는 가족도없다 연기못하는사람만모엿네</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>## 🔍 VOC 분석 보고서
+**[분석자 메모]** 본 민원은 서비스 이용상의 기술적 결함이 아닌, 콘텐츠 자체(배우 연기력 및 드라마의 서사/구성)에 대한 매우 강하고 부정적인 **평가성 의견**입니다. 극도의 불만 표출(Strong Negative Sentiment)이 특징이며, 감정적 대응보다는 콘텐츠 기획 부서의 검토가 필요한 사안입니다.
+---
+### 📝 1줄 요약 (Summary)
+배우 이응경과 길용우의 연기력 및 드라마의 스토리 구성(가족 부재, 반복적인 납치/감금 서사)에 대해 극도로 불만을 표출하며 콘텐츠의 질에 의문을 제기하는 부정적 평가 민원.
+---
+### 💡 대응 가이드 (Action Plan)
+**1. 분류 및 심각도 (Classification &amp; Severity)**
+*   **분류:** 콘텐츠/제작 품질 (Content/Production Quality)
+*   **심각도:** 중~상 (Moderate to High) - 비록 감정적인 표현이 강하지만, 핵심 시청층이 콘텐츠의 근본적인 재미와 완성도에 대해 회의를 느끼고 있음을 보여주는 중요한 지표임.
+**2. 대응 방향 (Action Strategy)**
+*   **[❌ 절대 하지 말아야 할 것]:** 감정적인 언사에 같이 맞서거나, 특정 배우를 비방하는 형태로 대응하는 것.
+*   **[✅ 권장 대응]:** 해당 피드백을 **콘텐츠/제작 부서에 전달하는 창구 역할**을 수행하고, 제작팀이 이 의견을 기획 검토 자료로 활용하도록 촉구함. (단순 민원 응대가 아님을 인지해야 함)
+**3. 내부 액션 플랜 (Internal Action Items)**
+| 담당 부서 | 주요 활동 내용 | 목적 |
+| :--- | :--- | :--- |
+| **콘텐츠 기획팀 / 제작팀** | **내부 회고 및 검토 요구** (Review Request) | 언급된 특정 배우의 연기적 강점/약점 및 서사 구조(가족 부재, 반복되는 갈등)가 시청자의 공감이나 몰입을 저해하고 있는지 재검토하도록 피드백 전달. |
+| **품질 관리팀 (QA)** | **관련 데이터 교차 분석** (Cross-Analysis) | 이 민원이 특정 시청자 집단(예: 2030 세대)에게만 나타나는 반응인지, 아니면 광범위하게 나타나는 품질 이슈인지 데이터 패턴을 확인. |
+| **운영/마케팅팀** | **반론 준비 및 소통 계획** | 극단적인 부정 피드백이 쌓이는 경우, 시청자 의견 수렴의 장을 마련하거나, 제작 의도를 설명하는 콘텐츠를 통한 긍정적인 소통 기회 마련 검토. |
+**4. 최종 결론 (Conclusion)**
+이 민원은 단순한 악성 댓글이 아니라, **시청자들이 기대하는 '서사적 깊이'와 '연기적 설득력'이 현재 콘텐츠에서 부족하다는 핵심적인 시장 요구(Market Demand)를 담고 있습니다.** 감정적 대응보다는 제작 과정의 피드백으로 적극 활용하는 것이 중요합니다.</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>15.82</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1395</v>
+      </c>
+      <c r="G17" t="n">
+        <v>88.18000000000001</v>
+      </c>
+      <c r="H17" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2회차</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>7</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>울면서 손들고 횡단보도 건널때 뛰쳐나올뻔 이범수 연기 드럽게못해</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>**[VOC 분석 보고]**
+**📌 1줄 요약 (요약/분류):**
+배우 이범수의 특정 장면(감정 연기) 연기력에 대한 강한 불만 및 부정적 평가가 접수됨.
+---
+**🛠 분석 가이드 및 대응 방안:**
+**1. VOC 분류 (Classification):**
+*   **카테고리:** 콘텐츠 피드백 (Creative/Artistic Critique)
+*   **분류 세부:** 연기력/표현력 평가 (Acting Performance)
+*   **감성 분석 (Sentiment):** 매우 부정적 (Negative)
+**2. 핵심 이슈 분석 (Key Insight):**
+*   본 민원은 서비스의 운영상의 오류(버그, 지연 등)가 아닌, **배우의 연기 스타일이나 감정 표현의 디테일에 대한 주관적인 평가**입니다.
+*   '드럽게 못해'와 같은 강한 비난은 시청자의 기대치와 실제 전달되는 연기 사이의 괴리에서 발생합니다.
+**3. 대응 및 조치 가이드 (Action Plan):**
+*   **🚨 내부 공유:** 해당 의견을 서비스 운영 부서가 아닌, 콘텐츠 기획팀(콘텐츠 개발/제작 부서)에 전달하여 추후 콘텐츠 개선 및 시청자 피드백 수집 자료로 활용하도록 보고해야 합니다.
+*   **🚫 즉각적 대응 지양:** 이 민원은 콘텐츠의 본질적인 예술적 영역에 대한 비판이므로, 운영팀 차원에서 즉각적인 사과나 해명은 불필요하며 오히려 감정싸움을 유발할 수 있습니다.
+*   **💡 모니터링 강화:** 특정 출연진이나 장면 관련 비판이 반복될 경우, 해당 작품의 시청자 만족도 지수를 별도로 모니터링하여 트렌드 변화를 파악하는 근거로 활용해야 합니다.</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1087</v>
+      </c>
+      <c r="G18" t="n">
+        <v>88.37</v>
+      </c>
+      <c r="H18" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2회차</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>8</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>취향은 존중한다지만 진짜 내생에 극장에서 본 영화중 가장 노잼 노감동임 스토리도 어거지고 감동도 어거지</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>## [사내 VOC 데이터 분석 보고]
+**1. 📝 민원 요약 (1 Line Summary)**
+고객은 해당 영화를 본 경험에 대해 극도의 지루함을 느끼며, 스토리의 개연성이나 감동 요소 모두 결여된 최악의 작품이라는 점을 강력히 불만 표출함.
+***
+**2. 📢 분석 및 대응 가이드**
+**① 분류 (Category):** 콘텐츠 품질 및 고객 경험 (Content Quality / Customer Experience)
+**② 내부 검토 의견 (Internal View):**
+* 본 민원은 영화 자체의 몰입도와 감성적 만족도에 관한 주관적인 평가이므로, **극장의 서비스 운영(장비, 인력 등) 결함으로 보기 어려움.**
+* 그러나 '극장에서 본 영화 중 가장 노잼'이라는 극단적인 표현은 해당 작품의 **관람객 경험 측면에서 큰 실패**를 경험했다는 점을 시사함.
+* **[분석 필요]** 해당 작품에 대한 부정적 피드백이 일회적인지, 아니면 일정 규모 이상의 리뷰와 결합하여 특정 콘텐츠의 품질 문제가 반복적으로 제기되는지 교차 분석이 필요함.
+**③ 대응 지침 (Action Plan):**
+1. **(응대 응대 매뉴얼 적용)** 고객의 강한 감정적 표현(노잼, 어거지)을 우선 경청하고, 취향의 영역임을 존중하는 톤앤매너를 유지하며 공감해 주는 것이 핵심입니다.
+2. **(반박 금지)** "개인의 취향일 뿐입니다"와 같은 내용으로 민원을 방어하거나 논쟁할 경우, VOC는 다시 악화될 수 있으므로 절대 사용하지 않습니다.
+3. **(선택적 후속 조치)** 사내 운영팀에서는 해당 영화의 평점 분포 및 관련 민원 빈도를 확인하여, 만약 특정 장르나 평점이 낮은 콘텐츠가 반복적으로 상영될 경우 향후 콘텐츠 큐레이션 시 참고 자료로 활용하도록 보고할 예정입니다.
+**[종합 결론]** 주관적인 호불호가 강한 영역이지만, 극단적인 부정적 경험은 잠재적 고객 이탈의 원인이 될 수 있으므로 **'고객의 부정적 감정 진화'**에 초점을 맞춘 공감적 대응이 필요합니다.</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1025</v>
+      </c>
+      <c r="G19" t="n">
+        <v>87.66</v>
+      </c>
+      <c r="H19" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2회차</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>9</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>굿바이 레닌 표절인것은 이해하는데 왜 뒤로 갈수록 재미없어지냐</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>## 📝 VOC 분석 리포트
+**🔍 핵심 요약 (1줄 요약):**
+작품의 주제(표절 요소)는 이해하나, 중후반부 전개 속도와 몰입도가 떨어져 재미가 감소했다는 서사적 만족도 저하 의견임.
+---
+**👩‍🏫 분석 및 가이드 (응대 전략):**
+**[관점]**
+- 고객은 콘텐츠의 창의성(표절 인지) 자체는 긍정적으로 인정했으나, *기대와 현실 간의 괴리*에서 지루함을 느꼈습니다.
+- 단순한 '재미 없음'이 아니라 '전개 속도/몰입도/후반부 완결성'에 대한 구체적인 불만을 제기한 것으로 해석해야 합니다.
+**[핵심 응대 전략]**
+1. **공감 및 경청:** 표절이나 주제 전달 자체에 대한 고객의 인정을 먼저 인정하며, 후반부 몰입도가 떨어진 점에 대해 깊이 공감해 드립니다. (방어적 태도 금지)
+2. **피드백의 수용:** "후반부 전개 속도나 구성에 아쉬움이 있었다"는 의견을 서비스 개선을 위한 중요한 VOC로 인식하고 기록합니다.
+3. **대안 제시 (선택 사항):** 이 콘텐츠를 통해 전달하려 했던 메인 메시지(예: 주제 의식, 깊이 등)를 간략히 설명하며, 그럼에도 불구하고 본 작품이 제공하고자 했던 가치를 한 번 더 제시해 드리는 방식으로 마무리할 수 있습니다.
+**[추천 답변 방향]**
+"굿바이 레닌의 주제와 독창적인 연출에 대해 긍정적으로 봐주셨는데, 말씀해주신 대로 후반부 전개 과정에서 재미가 다소 떨어지셨다면 저희가 의도했던 메시지가 전달되는 과정에서 몰입감에 아쉬움을 드린 것 같습니다. 고객님의 소중한 의견은 작품의 스토리텔링 완성도를 높이는 데 적극 반영하도록 하겠습니다."</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="F20" t="n">
+        <v>698</v>
+      </c>
+      <c r="G20" t="n">
+        <v>88.37</v>
+      </c>
+      <c r="H20" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2회차</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>10</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>재미없다 지루하고. 같은 음식 영화인데도 바베트의 만찬하고 넘 차이남....바베트의 만찬은 이야기도 있고 음식 보는재미도 있는데 ; 이건 볼게없다 음식도 별로 안나오고, 핀란드 풍경이라도 구경할랫는데 그것도 별로 안나옴 ㅡㅡ</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>## [VOC 분석 결과 보고]
+### 📝 1줄 요약
+작품의 몰입도 및 전반적인 재미가 낮고, 주요 콘텐츠인 음식 연출이나 배경(핀란드 풍경)의 시각적 매력이 기존 기대치와 비교하여 실망감을 주었음.
+***
+### 📈 VOC 분석 및 개선 가이드
+**📌 핵심 키워드:** 지루함, 재미 부족, 시각적 매력 결여 (음식, 풍경), 비교 우위(바베트의 만찬)
+#### 💡 분석 인사이트
+고객은 단순히 스토리가 아닌, 해당 작품의 정체성(음식, 미장센, 분위기)에서 오는 '경험의 질'을 기대하고 있습니다. 특정 경쟁작(바베트의 만찬)을 벤치마킹하며, 본 작품의 **'재미'가 서사뿐만 아니라 시각적 요소와 연출의 밀도에서 충분히 확보되지 못했다**고 평가합니다.
+---
+#### 🛠️ 조치 가이드 (Action Plan)
+**1. [콘텐츠/제작 부서 대상] 서사 및 속도(Pacing) 점검:**
+* **진단:** 지루하다는 피드백은 서사 전달의 밀도나 전개 속도에 문제가 있을 수 있습니다.
+* **조치:** 영화의 중반부 구간 등 지루함을 호소하는 특정 시퀀스를 재검토하여, 서사의 긴장감이나 몰입도를 높이는 장치(사건, 대화의 전환 등)를 강화할 필요가 있습니다.
+**2. [연출/미술 감독 대상] 시각적 경험 강화 (Food &amp; Scenery):**
+* **진단:** "음식도 별로 안 나온다," "풍경도 평범하다"는 지적은 시각적 기대치를 충족시키지 못했음을 의미합니다.
+* **조치:**
+    * **Food Styling:** 음식의 플레이팅이나 연출 컷의 디테일을 강화하여, 음식 자체를 하나의 '미적 오브제'로 활용하는 방식을 도입해야 합니다.
+    * **Cinematography:** 핀란드 풍경이 가진 고유의 분위기(Nordic Aesthetic)를 극대화할 수 있도록 카메라 구도, 조명 활용, 컬러 그레이딩 등의 영상 기법을 보강하는 방안을 검토해야 합니다.
+**3. [마케팅 부서 대상] 타겟팅 및 USP 재정립:**
+* **진단:** 고객은 '음식과 풍경'이라는 이 콘텐츠의 잠재적 매력을 기대하고 시청했으나 충족되지 않았습니다.
+* **조치:** 향후 홍보 시, 단순한 줄거리 소개를 넘어 **"어떤 시각적 경험(Visual Journey)"**을 제공하는지에 초점을 맞춘 키 비주얼과 카피를 사용하여 기대치와 실제 경험 간의 괴리를 줄여야 합니다. (예: "미식의 향연을 넘어, 북유럽의 평온함을 담다" 등)
+---
+**📝 최종 결론:**
+본 민원은 단순한 불만이 아니라, **높은 미적 기준(Aesthetic Standard)**을 가진 충성 고객층이 콘텐츠에서 원하는 **'경험의 밀도'**가 부족했음을 명확히 지적한 중요한 피드백입니다. 시각적 연출 강화에 최우선 순위를 두어야 합니다.</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>17.45</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1535</v>
+      </c>
+      <c r="G21" t="n">
+        <v>87.98</v>
+      </c>
+      <c r="H21" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3회차</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>아 더빙.. 진짜 짜증나네요 목소리</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>## 🎙️ 사내 VOC 분석 보고서
+**[분석자: VOC 데이터 분석팀]**
+**[작성일: 2023-10-27]**
+---
+### 📌 1줄 요약 (Summary)
+콘텐츠 내 더빙된 목소리의 톤이나 연기력에 대해 강한 불쾌감과 불만을 표출하는 VOC가 접수되었습니다.
+### 📝 대응 가이드 (Action Plan)
+본 VOC는 매우 감정적인 수준으로 작성되었으나, '더빙'이라는 특정 콘텐츠 요소에 대한 품질 저하 의견으로 분류하여 후속 조치를 진행해야 합니다.
+**1. 상황 확인 및 심층 분석 (Investigation)**
+*   **정보 보강 요청:** 해당 의견을 제기한 고객이 어떤 콘텐츠(제목, 에피소드, 특정 장면 등)를 시청했을 때 불만을 가졌는지 추가 정보를 확보해야 합니다.
+*   **데이터 교차 확인:** 해당 콘텐츠에 대한 다른 VOC(음향, 몰입감 관련)가 동시 접수되고 있는지 확인하여 해당 문제는 개별적인 불만인지, 시스템적 문제인지 판단합니다.
+**2. 즉각적인 조치 (Short-term Fix)**
+*   **내부 검토:** 콘텐츠 제작팀 또는 성우/더빙 담당 팀에 해당 장면의 음향 및 연기 디렉팅이 의도대로 이루어졌는지 자체 검토를 요청합니다.
+*   **피드백 수용:** 만약 연기 톤이나 품질에 객관적인 문제가 발견된다면, 차후 콘텐츠 개선(재편집 또는 더빙 재녹음 검토)이 필요할 수 있음을 염두에 둡니다.
+**3. 장기적 예방책 (Long-term Prevention)**
+*   **품질 가이드 강화:** 더빙 캐스팅 및 녹음 과정에 대한 내부 QC(Quality Control) 가이드라인을 재점검하고, 캐릭터 설정과 일치하지 않는 목소리가 배제될 수 있도록 프로세스를 강화해야 합니다.</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1133</v>
+      </c>
+      <c r="G22" t="n">
+        <v>87.58</v>
+      </c>
+      <c r="H22" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>3회차</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>너무재밓었다그래서보는것을추천한다</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>사내 VOC 데이터 분석가로서 해당 민원(고객 의견)을 분석하고, 경영진 및 관련 부서에 보고할 수 있는 요약 및 실행 가이드를 제시합니다.
+---
+### **🔎 VOC 분석 보고서**
+**1. 텍스트 원문:**
+"너무재밓었다그래서보는것을추천한다"
+**2. 1줄 요약 (Summary):**
+제품/서비스에 대한 극도의 만족감을 표현하며 강력하게 추천 의사를 밝히는 매우 긍정적인 피드백.
+**3. 분석 결과 및 가이드 (Action Guide):**
+**✅ 분석 등급:** ⭐ **High Positive (극호)**
+**✅ 핵심 키워드:** 만족, 추천, 긍정적 경험
+**[💡 가이드라인: 이 긍정적 데이터를 어떻게 활용할 것인가?]**
+| 영역 | 실행 방안 (Action Item) | 목표 및 기대 효과 |
+| :--- | :--- | :--- |
+| **✅ 마케팅 및 홍보** | **'입소문(Word-of-Mouth)' 사례 발굴 및 활용** | 해당 피드백을 기반으로 '고객 추천' 캠페인 자료로 활용하여 잠재 고객에게 신뢰도(Social Proof)를 제공. |
+| **✅ 제품/서비스 개발** | **만족 요소 리서치 (Root Cause Analysis)** | *어떤* 부분이 '너무 좋았는지' 구체적인 디테일을 파악하기 위한 추가 인터뷰(Follow-up Survey)를 진행하여, 강점을 정량화하고 핵심 성공 요인(Key Success Factor)을 도출. |
+| **✅ 운영 및 CS** | **긍정적 경험 관리(Experience Management)** | 이처럼 강력한 추천 의사를 보인 고객에게 감사 인사를 전달하고 후속 접점을 마련하여 충성 고객(Loyalty)으로 전환하는 기회로 활용. |
+**🔍 분석 의견:**
+본 의견은 단순한 칭찬을 넘어 고객이 타인에게 자발적으로 확산시키고 싶을 만큼 강력한 만족도를 경험했음을 의미합니다. 이 강력한 '추천의 힘'을 데이터로 잡고, 해당 성공 요소를 차기 기획에 반드시 반영해야 합니다.</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1114</v>
+      </c>
+      <c r="G23" t="n">
+        <v>87.63</v>
+      </c>
+      <c r="H23" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>3회차</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>교도소 이야기구먼 ..솔직히 재미는 없다..평점 조정</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>## 📝 사내 VOC 분석 보고서
+**🔍 요약 (1줄):**
+현재 제공되는 교도소 관련 콘텐츠의 흥미도가 매우 낮아 사용자가 콘텐츠 주제 및 평점 조정(만족도 하락)을 요구함.
+***
+**💡 가이드 및 분석 (VOC 담당 부서 전달용):**
+**1. 분류 (Category &amp; Tag):**
+*   **주요 분류:** 콘텐츠 품질 및 주제 불만 (Content Quality &amp; Theme Dissatisfaction)
+*   **세부 태그:** 흥미도 저하(Low Interest), 주제 적합성 미달(Theme Mismatch), 콘텐츠 다양성 요구(Content Diversity Demand)
+**2. 근본 원인 분석 (Root Cause Analysis):**
+*   **관련 주제에 대한 거부감:** 사용자에게 '교도소'라는 특정 소재는 높은 재미나 공감대를 제공하지 못하고, 오히려 지루함이나 부정적인 경험을 유발하고 있음.
+*   **콘텐츠 기대치 미충족:** 콘텐츠의 장르적 기대치(예: 재미, 감동, 몰입도)를 충족시키지 못하고 소재 자체가 독자에게 매력적으로 다가서지 못하고 있음.
+*   **정서적 소진 (Fatigue):** 해당 주제를 반복적으로 다루거나 깊이 있게 다루는 것에 대한 피로감이 누적되었을 가능성 있음.
+**3. 대응 및 개선 가이드 (Action Plan):**
+*   **단기 조치 (Immediate Action):**
+    *   해당 콘텐츠의 노출 비중 및 업데이트 주기를 잠시 모니터링하고, 사용자 반응(댓글, 이탈률 등)을 심층 분석하여 재가동 여부 판단.
+    *   해당 주제에 대한 사용자 피드백을 데이터베이스화하여 향후 콘텐츠 제작 시 **'부정적 반응 패턴'**으로 분류하여 학습.
+*   **중장기 조치 (Strategic Recommendation):**
+    *   **콘텐츠 테마 다각화 검토:** 현재의 '소수자/범죄/특정 상황' 중심의 콘텐츠 외에, 사용자들이 선호할 만한 다른 장르(예: 휴먼 드라마, 힐링, 에피소드 코미디 등)를 A/B 테스트하여 잠재적 수요 확인 필요.
+    *   **톤앤매너(Tone &amp; Manner) 재설정:** 만약 해당 소재를 유지한다면, 다루는 관점을 심각하거나 잔혹한 톤에서 **'반전', '인간적 성장', '유머'** 등 대중적 흥미를 유발할 수 있는 방향으로 변경하는 실험 필요.</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>13.53</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1202</v>
+      </c>
+      <c r="G24" t="n">
+        <v>88.84999999999999</v>
+      </c>
+      <c r="H24" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3회차</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>막 걸음마 뗀 3세부터 초등학교 1학년생인 8살용영화.ㅋㅋㅋ...별반개도 아까움.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>## [사내 VOC 데이터 분석 보고서]
+**분석 담당:** [VOC 데이터 분석가]
+**작성 일자:** 2024년 X월 X일
+---
+### 🔍 민원 요약 (1 Line Summary)
+영유아 및 초등 저학년 대상 콘텐츠(3~8세)의 완성도와 가치에 대한 전반적인 불만을 제기하고 있으며, 서비스 품질 저하에 대한 부정적 인식이 확인됨.
+### 💡 분석 및 개선 가이드 (Action Plan)
+**1. Pain Point 도출**
+*   **핵심 문제:** 타깃 연령대(3세~8세)의 콘텐츠가 사용자 기대 수준(Quality/Value)을 충족시키지 못하고 있다는 품질 불만입니다. '아까움'이라는 표현은 단순한 취향 문제가 아닌, 콘텐츠의 가치나 완성도가 낮다고 판단될 정도로 서비스에 대한 실망감이 높음을 시사합니다.
+*   **관련 부서:** 콘텐츠 기획팀, 제작팀, QA(품질 보증)팀
+**2. 중점 검토 사항 및 액션 플랜**
+| 단계 | 검토 목표 | 세부 실행 방안 | 기대 효과 |
+| :--- | :--- | :--- | :--- |
+| **1단계** | **현행 콘텐츠 감사 (Audit)** | 3~8세 대상의 기존 콘텐츠 리스트를 확보하고, 스토리, 시각적 요소, 교육적 가치(있을 경우) 등 체크리스트를 통해 정량적 품질 검토를 진행합니다. | 품질 문제의 유형(스토리 부족, 그래픽 저하 등)을 구체화할 수 있습니다. |
+| **2단계** | **타겟 니즈 재정립 (Target Needs)** | 경쟁사 및 업계 우수 콘텐츠 벤치마킹을 실시하고, 해당 연령대가 실제로 기대하는 콘텐츠의 수준(Aspirational Level)을 사용자 리서치(포커스 그룹 등)를 통해 재정의합니다. | 시장 트렌드에 맞는 콘텐츠의 기준을 확립할 수 있습니다. |
+| **3단계** | **품질 개선 우선순위 설정** | 품질이 낮다고 평가된 콘텐츠군을 우선순위로 설정하고, 리메이크 또는 리소스를 투입하여 개선 로드맵을 수립합니다. | 고객 만족도 하락을 즉각적으로 방지하고 신뢰도를 회복합니다. |
+**📌 결론:** 해당 피드백은 단순한 의견이 아니라, 핵심 타깃 고객층이 느끼는 **'콘텐츠 품질에 대한 명확한 신뢰 부족'** 신호로 해석하고, 콘텐츠 제작 및 품질 관리 기준을 재정립해야 합니다.</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>14.09</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1248</v>
+      </c>
+      <c r="G25" t="n">
+        <v>88.55</v>
+      </c>
+      <c r="H25" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3회차</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>원작의 긴장감을 제대로 살려내지못했다.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>**[VOC 분석 보고] 원작 긴장감 재현 불만**
+안녕하십니까. 사내 VOC 데이터 분석가입니다. 접수된 민원에 대해 요약 및 대응 가이드를 다음과 같이 제출합니다. 본 민원은 단순한 불만을 넘어, **'원작의 핵심 가치(Source Fidelity)'가 최종 콘텐츠에서 손실되었다**는 치명적인 품질 지적에 해당합니다.
+---
+### 📄 1줄 요약 (VOC Summary)
+**[원작 충실도/몰입감] 원작 고유의 서사적 긴장감과 감정적 밀도(Tone &amp; Tension)를 성공적으로 재현하지 못한 것에 대한 강한 불만.**
+### 💡 분석 및 대응 가이드 (Action Guide)
+이와 같은 '긴장감 상실' 피드백은 시청자/독자가 콘텐츠의 가장 중요한 핵심 동력(Drive)을 느끼지 못했음을 의미합니다. 창작진 및 기획 부서에서는 다음의 세 가지 영역을 면밀히 재점검해야 합니다.
+#### 🔍 1. 근본 원인 진단 (Diagnosis)
+*   **원작 이해도 문제:** 제작진이 원작이 의도한 '긴장감'의 종류(심리적, 서사적, 액션 등)를 정확히 파악했는지 확인해야 합니다. 단순히 내용을 옮긴 것이 아니라, **원작의 '감정선과 결'**을 추출했는지 점검이 필요합니다.
+*   **연출/극본 문제:** 긴장감을 조성하는 핵심 장치(Pacing, 대사, 미장센, 사운드 디자인)가 약했거나 너무 쉽게 해소되었을 가능성이 높습니다. (예: 중요한 갈등이 너무 빨리 봉합됨)
+*   **대상과의 괴리:** 원작의 긴장감이 특정 장르적 특성에 기대는 경우, 그것이 새로운 매체(영화, 드라마 등)로 번역되는 과정에서 그 에너지가 분산되거나 약화되었을 수 있습니다.
+#### 🛠️ 2. 즉각적 개선 및 후속 조치 (Remedy)
+*   **핵심 포인트 재점검:** 원작 중 가장 긴장감이 폭발하는 장면이나 문장을 선정하여, 해당 장면의 **'연출 의도와 원작의 원본 감정 상태'**를 비교 분석하고 차이를 확인해야 합니다.
+*   **Pacing 점검:** 서사의 속도(Pacing)를 재조정해야 합니다. 긴장감이 느껴지려면 어느 정도의 '간격(Tension build-up)'이 필요합니다. 불필요하게 빠른 전개는 긴장감을 희석시킵니다.
+*   **외부 전문가 검토 도입:** 원작 팬이거나, 해당 장르의 연출에 강한 외부 평론가에게 **'긴장감 및 몰입도'**에 대한 추가 피드백을 요청하여 3차 검수를 진행합니다.
+#### 📈 3. 시스템적 예방 방안 (Prevention)
+*   **[Pre-Production 체크리스트] 긴장감/감정 지도(Emotional Map) 작성:** 제작 초기 단계부터 원작의 핵심 감정 흐름(Tension Points)을 시각적으로 매핑하고, 각 지점에서 어떤 연출적 장치(음악, 편집, 대사)가 긴장감을 극대화할지 정의하는 프로토콜을 표준화해야 합니다.
+*   **피드백 채널 강화:** 원작의 고충을 가장 잘 아는 소수(원작자, 핵심 팬)를 초기 컨설턴트로 영입하여 제작 과정 전반에 걸쳐 **'충실도의 모니터링'**을 의무화할 것을 제언합니다.
+---
+*본 분석은 향후 유사 VOC 발생 시 효율적인 대응을 위한 데이터 축적의 일환입니다. 추가적인 자료가 있을 경우 재분석해 드리겠습니다.*</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1568</v>
+      </c>
+      <c r="G26" t="n">
+        <v>88.70999999999999</v>
+      </c>
+      <c r="H26" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3회차</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>6</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>별 반개도 아깝다 욕나온다 이응경 길용우 연기생활이몇년인지..정말 발로해도 그것보단 낫겟다 납치.감금만반복반복..이드라마는 가족도없다 연기못하는사람만모엿네</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>**[사내 VOC 데이터 분석 보고서]**
+**데이터 요약 (1줄)**
+배우들의 연기력 부족 및 극의 반복적인 전개(납치/감금 위주의 플롯)에 대한 극도로 부정적이고 격앙된 비판이 접수됨.
+---
+**가이드 및 후속 조치 방안**
+**1. 핵심 키워드 및 감성 분석**
+*   **핵심 키워드:** 연기력 (이응경, 길용우), 플롯 (납치, 감금), 몰입도, 가족 부재.
+*   **감성:** 극도로 분노함 (Strong Negative), 실망함 (Disappointed).
+*   **분석:** 단순한 호불호를 넘어, 시청자가 드라마의 **근본적인 구성(배우와 서사)** 자체에서 만족을 얻지 못하고 있음을 시사하는 강한 거부감의 표출입니다.
+**2. 유관 부서 액션 플랜**
+| 담당 부서 | 검토/조치 사항 | 세부 실행 가이드 |
+| :--- | :--- | :--- |
+| **기획/제작팀 (Creative)** | **플롯의 차별성 및 깊이 검토** | '납치-감금' 등 클리셰적 소재의 반복 사용이 시청자를 지치게 할 수 있음. 서사에 **캐릭터 고유의 갈등**과 **동기 부여**를 추가하여 서사의 깊이를 확보해야 합니다. |
+| **캐스팅/연출팀 (Talent/Director)** | **배우 연기 톤 및 디테일 점검** | 특정 배우들의 연기 스타일이 캐릭터의 서사에 적절하게 녹아들지 못하고 있다는 지적이 있습니다. 연출 과정에서 **캐릭터의 현실적/감정적 디테일**을 강화하는 지도를 재실시할 필요가 있습니다. |
+| **마케팅/PR팀 (Marketing)** | **리스크 모니터링 및 대응** | 해당 민원은 매우 강한 부정적 어조를 띠고 있어, 커뮤니티 내 다른 부정적 여론으로 확산될 위험이 높습니다. 현재 콘텐츠의 장점(USP)을 부각하며 시청자 경험을 재조명하는 방향으로 커뮤니케이션 가이드라인을 점검해야 합니다. |
+**3. 분석 제언**
+*   단편적인 연기 비판을 넘어, **극의 구조(Structure)와 서사(Narrative)** 전반에 걸친 근본적인 피드백으로 해석해야 합니다. '연기 못하는 사람만 모였다'는 지적은 배우의 역량 문제일 수도 있으나, 이는 작가가 부여한 **캐릭터의 설득력 부족**에서 기인할 가능성이 높습니다.
+*   후속 회차에서는 감정선과 서사의 긴장감을 높이는 연출이 반드시 필요해 보입니다.</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1263</v>
+      </c>
+      <c r="G27" t="n">
+        <v>88.12</v>
+      </c>
+      <c r="H27" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>3회차</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>7</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>울면서 손들고 횡단보도 건널때 뛰쳐나올뻔 이범수 연기 드럽게못해</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>## 📊 VOC 분석 보고서
+**작성자:** 사내 VOC 데이터 분석가
+**일자:** 202X. XX. XX.
+---
+### 🎤 1줄 요약 (Summary)
+배우 이범수의 특정 장면(횡단보도 연기)에 대한 시청자의 연기력 불만 및 강한 부정적 감정 표출.
+---
+### 🔎 분석 가이드 (Guidance)
+**1. VOC 유형 분류 (Classification):**
+*   **주요 분류:** 비즈니스 외 의견 (Off-Topic) / 엔터테인먼트/콘텐츠 피드백
+*   **감정 분석:** 부정적 (High Negative Sentiment)
+*   **분석 키워드:** 이범수, 연기, 연기력, 불만
+**2. 중요도 및 조치 필요성 (Action Required):**
+*   **회사 연관성 확인:** 해당 피드백이 당사 서비스/제품/운영과 직접적인 관련이 없는 외부 콘텐츠(드라마, 영화 등)에 대한 비평일 경우, 내부 조치 필요성은 **낮음**.
+*   **엔터테인먼트 관련 부서 연관 시:** 만약 당사가 해당 배우의 에이전시 또는 제작사라면, 이 피드백을 **창작/연출팀 또는 배우 매니지먼트팀**에 전달하여 연기 코칭이나 다음 작품 참고 자료로 활용할 수 있습니다.
+**3. 대응 방안 (Response Strategy):**
+*   **외부 VOC 채널일 경우:** 이 의견은 콘텐츠 비평 영역이므로 직접적인 응대보다 해당 데이터를 축적하여 트렌드 변화(예: 특정 배우에 대한 대중의 기대치 변화)를 파악하는 데 활용하는 것이 적절합니다.
+*   **결론:** 당사의 직접적인 서비스 개선 방향과 무관한 의견으로 분류하고, 추후 데이터 분석 시 '콘텐츠 피드백' 항목으로 별도 분류하여 관리할 것을 권고합니다.</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1125</v>
+      </c>
+      <c r="G28" t="n">
+        <v>88.31999999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3회차</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>8</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>취향은 존중한다지만 진짜 내생에 극장에서 본 영화중 가장 노잼 노감동임 스토리도 어거지고 감동도 어거지</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>## [VOC 분석 보고서] 영화 관람 후 부정적 피드백
+**분석자:** VOC 데이터 분석팀
+**분석 대상:** 영화 관람 후 만족도 관련 민원
+---
+### 📝 1줄 요약 (Summary)
+**영화의 스토리 구성 및 감정 전달력 부족에 대한 강한 불만 표출로, 관람 경험 전반의 만족도가 극도로 낮음.**
+### 💡 VOC 가이드 및 분석 (Analysis &amp; Guidelines)
+#### 1. 🔍 핵심 키워드 및 감성 분석 (Keywords &amp; Sentiment)
+*   **핵심 불만:** 노잼(지루함), 노감동(감정 부재), 어거진 스토리(서사 구조/구성 문제).
+*   **감성 분석:** 매우 부정적 (Strong Negative). 단순한 선호도 차이를 넘어 '재미'와 '감동'이라는 핵심 경험 자체의 결여를 지적하고 있음.
+*   **특징:** 주관적인 취향 언급(취향은 존중한다)을 전제로 하되, 그 경험이 기대치를 크게 밑돌았음을 강조하는 형태임.
+#### 2. 🎯 대응 전략 (Response Strategy)
+**A. [운영/상품 측 관점] (Action Item: Content Quality)**
+*   **Pain Point 파악:** 고객은 '콘텐츠의 완성도' (스토리, 연출, 감정적 공감) 측면에서 가장 큰 실망을 느낌.
+*   **후속 조치 필요:** 단순히 관람 태도의 문제가 아닌, 상영작의 콘텐츠 자체에 대한 피드백으로 분류해야 합니다. 이 피드백은 향후 콘텐츠 선정 또는 QA 과정에서 참고 자료로 활용되어야 합니다. (다만, 개별 영화의 완성도를 회사 차원에서 100% 책임지기는 어려우므로, '콘텐츠 큐레이션' 관점에서 참고할 필요가 있습니다.)
+**B. [고객 응대 측 관점] (Action Item: Customer Service)**
+*   **공감 및 경청:** 고객의 강한 불만(노잼, 노감동)을 절대 가볍게 여기지 않고, 충분히 불편함을 공감해주는 자세가 필수적입니다.
+*   **대응 문구 가이드:**
+    *   (X) "개인의 취향 차이일 수 있습니다." (방어적)
+    *   (O) "고객님께서 느끼신 스토리의 개연성이나 감정적 몰입도가 낮았던 점에 대해 안타까움을 표하며, 저희가 선별한 콘텐츠가 기대에 미치지 못해 죄송합니다." (공감 기반의 사과)
+*   **중요:** 해당 민원이 다른 관람객에게 '이 영화는 재미없다'는 부정적 입소문을 유발할 수 있으므로, 내부적으로는 민원 처리 후 관람 환경 개선(예: 좌석, 청각 환경 점검)으로의 연계는 최소화하고, 피드백 수용 차원에서 대응합니다.
+#### 3. 📋 내부 분류 태그 (Internal Tagging)
+`#콘텐츠불만 #서사결함 #만족도저하 #영화경험`</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1378</v>
+      </c>
+      <c r="G29" t="n">
+        <v>88.15000000000001</v>
+      </c>
+      <c r="H29" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3회차</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>9</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>굿바이 레닌 표절인것은 이해하는데 왜 뒤로 갈수록 재미없어지냐</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>## 🔍 VOC 데이터 분석 보고서
+**분석자:** 사내 VOC 데이터 분석가
+**분석 일자:** 2023. 11. 27.
+**분석 대상:** 시청자 불만 사항 (굿바이 레닌 모작 콘텐츠)
+---
+### 1. 🎤 1줄 요약 (Summary)
+후반부로 갈수록 내용의 **서사적 몰입도(Pacing)**가 급격히 저하되어 재미가 없다는 불만이며, 원작(굿바이 레닌)과의 비교를 통해 완성도에 대한 기대치를 표출하고 있음.
+---
+### 2. 💡 개선 가이드 및 액션 플랜 (Guideline &amp; Action Plan)
+본 피드백은 콘텐츠의 초반적인 매력이나 설정 자체는 수용되지만, **'지속 가능한 재미'**와 **'엔딩의 만족도'**가 부족하다는 핵심적인 지적입니다. 제작 및 기획 단계에서 다음과 같은 점을 중점적으로 점검해야 합니다.
+#### ✅ **[긴급 진단 영역: 서사 및 연출]**
+1.  **후반부 동력(Momentum) 확보:**
+    *   **문제점:** 후반부에서 주요 갈등 해소나 변화가 정체되며 속도가 느려지고 있을 가능성이 높습니다.
+    *   **개선 방안:** 결말이 다가올수록 긴장감을 해소하기보다 오히려 새로운 위기나 의외의 변수(Twist)를 던져 시청자의 예측 범위를 벗어나게 해야 합니다.
+2.  **'감정적 보상(Emotional Payoff)' 강화:**
+    *   **문제점:** 초반부에 부여한 몰입 요소(설정, 캐릭터의 매력 등)가 결말에서 충분히 보상받지 못하고 맥없이 사라지고 있을 수 있습니다.
+    *   **개선 방안:** 시청자가 초반에 투자한 감정적 에너지를 결말에서 확실하게 회수해주는 강력한 클라이맥스나 카타르시스를 설계해야 합니다.
+3.  **템포 및 밀도 조절:**
+    *   **문제점:** '늘린다'는 이유로 불필요한 설명이나 반복적인 장면이 삽입되어 피로도가 높아졌을 수 있습니다.
+    *   **개선 방안:** 현재 진행 속도(Pacing)를 점검하고, 핵심적인 스토리 진행과 감정의 교차 지점에는 속도를 올리고, 불필요한 장면은 과감하게 쳐내야 합니다.
+#### 📝 **[추가 제언: 데이터 활용]**
+*   **시청 이탈 지점 확인:** 해당 콘텐츠의 실제 시청 데이터를 분석하여, 시청자들이 실제로 재미를 느끼지 못하고 이탈하는 구간(Drop-off point)이 **후반부 어느 시점**인지를 객관적인 수치로 확인하는 것이 가장 중요합니다.
+*   **A/B 테스트:** 다음 콘텐츠 기획 시, **후반부 시나리오 버전**에 대한 시뮬레이션(테스트)을 진행하여 '엔딩의 힘'을 미리 측정할 것을 권고합니다.
+---
+**[작성 메모]**
+*이번 민원은 단순한 '불만'을 넘어 콘텐츠의 **'지속 가능성(Sustainability)'**에 대한 근본적인 질문입니다. 제작팀은 초기 흥행 동력을 후반부까지 유지하는 '엔딩 설계'에 리소스를 집중해야 합니다.*</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1491</v>
+      </c>
+      <c r="G30" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="H30" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>3회차</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>10</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>재미없다 지루하고. 같은 음식 영화인데도 바베트의 만찬하고 넘 차이남....바베트의 만찬은 이야기도 있고 음식 보는재미도 있는데 ; 이건 볼게없다 음식도 별로 안나오고, 핀란드 풍경이라도 구경할랫는데 그것도 별로 안나옴 ㅡㅡ</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>## 🎥 VOC 분석 보고서
+**작성자:** 사내 VOC 데이터 분석가
+**분석 일시:** 2023-11-16
+---
+### 🔍 민원 요약 (1줄 요약)
+**음식과 배경 등 시각적 볼거리 및 몰입도가 현저히 떨어져, 기대했던 재미를 느끼지 못하고 지루함을 느낀다는 불만.**
+---
+### 📋 담당 부서 및 담당자 가이드
+**[담당 부서] 콘텐츠 제작팀 / 상품 기획팀**
+**[핵심 요청사항] 시각적 임팩트 및 스토리 보완**
+#### 💡 **VOC 분석 가이드 및 액션 플랜**
+본 민원은 단순히 ‘취향의 차이’를 넘어, **'콘텐츠의 본질적인 차별성 부재'**에 대한 고객의 직접적인 비판입니다. 고객은 타 경쟁작(비교 대상)과의 확실한 매력 포인트(음식, 풍경, 스토리)가 부족하다고 명시했습니다. 이에 아래와 같은 구체적인 후속 조치를 권고합니다.
+1.  **[콘텐츠 검토/회고] 시각적 요소 및 밀도 점검:**
+    *   **요구사항:** 단순히 '배경이 있다' 수준이 아닌, '시선을 사로잡는' 수준의 미장센 및 영상미 보완 필요.
+    *   **실행 방안:** 음식의 재현 방식(컬러, 질감 등)이나 핀란드의 지형적 아름다움을 극대화할 수 있는 구도 및 촬영 기법을 재검토하고, 후속 영상이나 패키징에 해당 요소를 강화할 아이템을 발굴해야 함.
+    *   **핵심 질문:** 다른 고객에게도 이 정도의 '비주얼적 만족감'을 줄 수 있는 지점은 어디인가?
+2.  **[경쟁사 분석 심화] 강점 비교 대조:**
+    *   **요구사항:** 고객이 언급한 비교 대상 영화('바베트의 만찬' 등)의 성공 요소를 세부적으로 분석하여 본 콘텐츠에 적용 가능한 요소를 도출해야 함.
+    *   **실행 방안:** 경쟁사 콘텐츠의 **'서브 콘텐츠(음식, 풍경 등)'**가 어떻게 스토리를 보조하며 고객의 흥미를 유지시키는지 데이터화하고, 현재 부족한 부분이 어디인지 명확히 파악하여 콘텐츠 보완 방향을 수립하십시오.
+3.  **[후속 대응/A/B 테스트] 개선점 반영 여부 확인:**
+    *   **요구사항:** 해당 피드백을 단순 참고 사항으로 남기지 않고, 다음 업데이트 또는 마케팅 전략에 반영했는지 확인해야 합니다.
+    *   **실행 방안:** 콘텐츠의 핵심 시각적 매력 요소를 강조하는 새로운 티저나 리뷰 가이드를 제작하고, 이를 통해 고객들이 기대했던 '음식의 재미'와 '배경의 아름다움'을 미리 시각적으로 인지하고 몰입할 수 있도록 유도하는 전략이 필요합니다.</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1328</v>
+      </c>
+      <c r="G31" t="n">
+        <v>86.81999999999999</v>
+      </c>
+      <c r="H31" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>4회차</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>아 더빙.. 진짜 짜증나네요 목소리</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>## [VOC 분석 리포트]
+### 🎙️ 1줄 요약
+**콘텐츠 내 더빙(Voice Over) 목소리의 품질 및 만족도에 대한 부정적 불만이 제기됨.**
+***
+### 🧭 대응 및 조치 가이드
+**🎯 목표:** 해당 불만이 단순한 개인의 취향 문제인지, 아니면 제품/서비스의 핵심 품질(Quality) 문제인지를 파악하고, 개선이 필요한 경우 구체적인 해결책을 제시합니다.
+#### 🔍 1단계: 현상 파악 및 데이터 보강 (Triage &amp; Data Collection)
+* **심층 분석:** 해당 민원이 단발성인지, 아니면 특정 버전/특정 콘텐츠에 집중된 패턴인지 전체 VOC 데이터를 교차 분석해야 합니다. (추가적인 관련 키워드: '오디오', '음성', '배경음', '톤', '목소리' 등을 키워드 검색)
+* **구체적 정보 요청:** 민원인에게 어떤 부분(발음, 톤, 성우 캐스팅, 녹음 품질 등)이 짜증 났는지 구체적인 피드백을 요청하여 근거 자료를 확보해야 합니다.
+#### 🛠️ 2단계: 원인 진단 (Root Cause Analysis)
+다음 항목들을 점검하여 불만의 원인을 세 가지 측면에서 진단합니다.
+* **A. 캐스팅/콘텐츠 측면:** 더빙의 성우 발화가 캐릭터의 역할이나 상황에 부적절한가? (Script 및 Voice Acting Direction 오류)
+* **B. 기술/품질 측면:** 녹음 상태, 오디오 믹싱 볼륨, 음질 자체가 낮은가? (Technical QA 이슈)
+* **C. 사용자 기대치 측면:** 사용자의 기대치와 해당 제품의 현 수준 간의 괴리가 큰가? (시장/경쟁사 비교 필요)
+#### 💡 3단계: 전략적 개선 방안 (Action Plan)
+* **단기 대응 (Quick Fix):**
+    * 해당 콘텐츠의 오디오 파일에 대한 **QA(Quality Assurance) 재점검**을 긴급 실시하고, 오디오 믹싱(Volume, EQ)을 조정하는 방안을 검토합니다.
+    * 불만이 심한 경우, 관련 패치나 업데이트 시 음질 개선을 최우선 순위에 배치합니다.
+* **장기 대응 (System Improvement):**
+    * 향후 콘텐츠 제작 시, **사전 성우 및 오디오 품질 검수 체크리스트**를 의무화하고, 사용자 피드백을 초기 단계에 반영하는 프로세스를 구축합니다.
+    * 더빙 및 음성 콘텐츠에 대한 사용자 만족도 지표(Voice/Audio Satisfaction Score)를 VOC 분석 항목에 추가하여 주기적으로 모니터링합니다.</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1309</v>
+      </c>
+      <c r="G32" t="n">
+        <v>87.52</v>
+      </c>
+      <c r="H32" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>4회차</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>너무재밓었다그래서보는것을추천한다</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>**[분석가 톤 및 형식으로 작성]**
+---
+### 📝 민원 요약 및 분석 가이드
+**1. 🔍 1줄 요약 (핵심 감정 및 내용)**
+*   **[추천/극찬]** 서비스/제품에 대한 만족도가 매우 높으며, 강력하게 타인에게 추천하고 싶다는 긍정적 피드백을 전달함.
+**2. 🧭 분석 및 후속 조치 가이드 (Action Plan)**
+**A. 긍정적 강화 분석 (Reinforcement)**
+*   **핵심 목표:** 고객이 어떤 요소 때문에 '재미있다'고 느꼈는지 구체적인 **핵심 성공 요인(Key Success Factor)**을 도출해야 함.
+*   **질문 사항:** (만약 다른 데이터가 있다면) 고객이 언급한 특정 기능, 콘텐츠, 경험 중 가장 높은 점수를 받은 요소는 무엇인가? (e.g., UX의 직관성, 내용의 몰입도, 사용자 인터페이스 등)
+*   **활용 방향:** 이 긍정적인 경험을 마케팅 자료(Testimonial)로 활용하여 바이럴 마케팅의 소재로 즉시 활용 검토.
+**B. 데이터 패턴 탐색 (Trend Detection)**
+*   **핵심 목표:** 이번 피드백이 우발적인 만족인지, 반복적인 사용자 경험의 결과인지 파악해야 함.
+*   **조치 사항:** 해당 피드백을 제기한 고객의 이용 패턴(사용 기간, 방문 빈도, 이용한 메뉴)을 확인하고, 비슷한 긍정 평가를 남긴 다른 사용자들의 피드백과 **연관성(Correlation)** 분석을 진행할 것.
+**C. 내부 공유 및 프로세스 적용 (Internal Application)**
+*   **핵심 목표:** 긍정적인 경험의 원인을 해당 부서에 전달하여 서비스 표준으로 정착시키는 것이 중요함.
+*   **조치 사항:** 해당 칭찬 피드백을 담당 부서(콘텐츠 기획, 개발, 운영 등)에 공유하며, 해당 긍정 요소를 **'Best Practice'**로 기록하고 다음 업데이트나 개선 방향에 참고할 것을 권고.</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1129</v>
+      </c>
+      <c r="G33" t="n">
+        <v>86.31999999999999</v>
+      </c>
+      <c r="H33" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>4회차</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>교도소 이야기구먼 ..솔직히 재미는 없다..평점 조정</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>## 사내 VOC 데이터 분석 결과 보고
+### 📋 핵심 요약 (One-Line Summary)
+*   **콘텐츠(교도소 소재)의 흥미도 및 몰입감 부족에 대한 부정적 의견이 제기되었으며, 이에 따른 평가(점수) 하향을 요청하고 있음.**
+***
+### 💡 분석 및 대응 가이드 (Analysis &amp; Action Guide)
+**1. 데이터 유형 및 의도 분석**
+*   **유형:** 만족도/품질 저하 피드백 (감성/주관적 만족도)
+*   **주요 키워드:** 교도소, 재미 없음, 평점 조정
+*   **분석 의도:** 특정 콘텐츠(혹은 서비스 영역)의 '엔터테인먼트 가치'에 대한 고객 불만 표출. 단순히 소재의 문제라기보다는 **콘텐츠의 구성, 연출, 스토리가 고객의 기대치(재미)를 충족시키지 못했다**는 의미로 해석됨.
+**2. 대응 전략 (Action Plan)**
+*   **A. 콘텐츠 검토 (Content Review):**
+    *   해당 콘텐츠의 시청자/사용자 반응(데이터)을 확인하여 ‘재미가 없다’고 느끼는 구체적인 지점(예: 지루한 전개, 진부한 설정 등)이 있는지 내부적으로 분석한다.
+    *   만약 정기적으로 유사한 콘텐츠를 제공한다면, 콘텐츠 기획 단계에서 **'엔터테인먼트 요소'와 '지루함' 사이의 균형**을 점검하는 가이드라인을 마련해야 한다.
+*   **B. 피드백의 수용 및 기록 (Feedback Incorporation):**
+    *   해당 고객의 피드백을 **'콘텐츠의 몰입도 저하'** 지표로 기록하고 추적한다. 이는 향후 신규 콘텐츠 제작 시 기획 타당성 검토 자료로 활용한다.
+*   **C. 대응 수위 결정 (Response Strategy):**
+    *   개별적인 평가 하향 요청에 대해 즉각적인 점수 조정을 제공하기보다는, **'고객님의 소중한 의견을 접수했으며, 콘텐츠의 만족도 개선을 위한 검토가 이루어질 것'**임을 안내하며 피드백의 수용 의지를 보여주는 것이 바람직함.
+**✅ [담당팀 참고 사항]**
+이 민원은 *‘서비스 불편’*보다는 *‘콘텐츠의 품질(Quality of Content)’*에 대한 지적입니다. 콘텐츠 제작 및 기획 담당 부서와의 소통 채널을 통해 해당 소재의 활용 가치와 재미 포인트를 재점검하시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="F34" t="n">
+        <v>951</v>
+      </c>
+      <c r="G34" t="n">
+        <v>88.67</v>
+      </c>
+      <c r="H34" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>4회차</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>막 걸음마 뗀 3세부터 초등학교 1학년생인 8살용영화.ㅋㅋㅋ...별반개도 아까움.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>## 🎥 VOC 분석 보고서
+### 📋 1. 요약 (1-Line Summary)
+어린이(3~8세) 대상 영화의 콘텐츠 품질 및 만족도가 기대치에 미치지 못하며 전반적인 아쉬움을 표현함.
+***
+### 🔍 2. 분석 가이드 (Action Plan)
+**[VOC 분류]**
+* **주제:** 콘텐츠 및 상품 품질 (Content &amp; Quality)
+* **세부 이슈:** 타겟 연령층(3~8세)의 흥미 및 몰입도 저하, 기대 이하의 작품성.
+* **강도:** 중간 (직접적인 비판을 통해 상품 가치에 의문을 제기함.)
+**[분석 팀 및 담당 부서]**
+* **1차 분석:** 콘텐츠 기획팀 / QA팀
+* **2차 대응:** 마케팅팀 (상품 포지셔닝 재점검)
+**[권고 조치 및 액션 아이템]**
+1. **콘텐츠 품질 검수 강화 (Content Audit):**
+    * 현재 해당 연령대에 배포된 영화들의 **실제 관람객 리뷰 및 별점 데이터**를 교차 분석하여, 이 민원이 특정 작품에 국한된 것인지 전반적인 트렌드인지 확인해야 합니다.
+    * '3세부터 8세용'이라는 타겟 설정이 해당 연령층의 **최소한의 흥미 요소(몰입도, 메시지, 시각적 자극)**를 충족하는지 전문 검수자(Target Group Representative)를 통한 재평가가 필요합니다.
+2. **경쟁사 대비 포지셔닝 재정립 (Competitive Benchmarking):**
+    * 경쟁사에서 성공적으로 포지셔닝하고 있는 유사 연령대 영화의 **특징(스토리 구조, 영상미, 교육적 요소 등)**을 조사하여, 우리 제품이 놓치고 있는 핵심 매력 요소를 파악합니다.
+3. **사용자 경험(UX) 측면 보완 (Refining Target Persona):**
+    * 만약 '3세'부터 '8세'까지 폭넓게 설정했다면, 연령대별 니즈가 다름을 인지해야 합니다. (예: 3세는 단순한 색감/움직임, 8세는 복잡한 서사와 성장 서사 요구). 연령대별 서브 카테고리(예: 'Pre-School', 'Early Reader')를 구분하여 기획의 정밀도를 높여야 합니다.
+**➡️ [요약 결론]**
+단순한 감상평을 넘어, **타겟 콘텐츠의 가치와 질이 시장의 기대치(Expectation) 대비 미달**하고 있음을 시사합니다. 콘텐츠 기획의 **'정밀도'**를 높이는 작업이 시급합니다.</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1195</v>
+      </c>
+      <c r="G35" t="n">
+        <v>87.06999999999999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>4회차</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>5</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>원작의 긴장감을 제대로 살려내지못했다.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>## 🎤 VOC 데이터 분석 보고서
+**분석 담당:** [분석가 이름/직함]
+**일자:** 202X. XX. XX.
+---
+### 📝 1줄 요약 (VOC Summary)
+&gt; 원작의 핵심 서사적 긴장감 및 몰입도 구현 실패에 대한 품질 관련 불만 제기.
+---
+### 💡 분석 가이드 및 대응 전략 (Analysis &amp; Action Guide)
+**1. 🔍 핵심 분석 및 인사이트 (Analysis)**
+*   **불만 유형:** 콘텐츠의 연출/재현 품질 이슈 (Creative Execution / Quality Gap).
+*   **핵심 키워드:** 긴장감 (Tension), 원작 충실도 (Fidelity), 서사적 몰입감 (Immersion).
+*   **의미하는 바:** 단순히 내용이 이해되지 않는 것이 아니라, **원작이 구축해 놓은 감정적, 서사적 압박감(Suspense)**을 매체(영상, 번역, 각색 등)가 성공적으로 전달하지 못했다는 지적입니다. 이는 콘텐츠의 가장 기본적인 매력 요소(Killer Feature)가 훼손되었다고 볼 수 있습니다.
+**2. 🎯 대응 액션 플랜 (Action Plan)**
+| 단계 | 목표 | 세부 실행 항목 | 담당 부서 |
+| :--- | :--- | :--- | :--- |
+| **진단 (Diagnose)** | 원작 대비 차이점 파악 | 원작과 제작물(각색본 등)의 장면별, 감정선별(Pacing, Dramatic Arc) 비교 분석을 실시하여 긴장감을 저해하는 지점(Punto of Failure)을 정확히 찾아야 함. | 콘텐츠 기획/제작팀 |
+| **개선 (Improve)** | 긴장감 재구축 방안 모색 | **(단기)** 해당 파트에 대한 후속 보완 작업 (예: 편집, 음향, 연출 수정 등) 필요성 검토. &lt;br&gt; **(장기)** 향후 기획 단계에서 '긴장감 유지'를 핵심 KPI로 설정하고, 원작 저자가 의도한 **'절박함(Stakes)'**을 유지할 수 있는 가이드라인을 수립해야 함. | 기획/연출팀 |
+| **피드백 (Feedback)** | 고객 인식 확인 | 유사한 불만 제기가 발생하는지 VOC DB 전반을 교차 분석하여, 특정 연출 문제인지 혹은 전반적인 집필/각색 기조의 문제인지를 구분해야 함. | VOC 분석팀 |
+**3. 📊 우선순위 및 심각도 (Priority &amp; Severity)**
+*   **우선순위:** 높음 (High). 원작 충실도는 팬덤 및 충성 고객 만족도에 직결되는 핵심 지표임.
+*   **심각도:** 보통~높음 (Medium to High). 단순 연출 이슈를 넘어, 매체의 본질적인 가치 전달 실패로 이어질 경우 이탈률 증가로 직결됨.</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1313</v>
+      </c>
+      <c r="G36" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="H36" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>4회차</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>6</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>별 반개도 아깝다 욕나온다 이응경 길용우 연기생활이몇년인지..정말 발로해도 그것보단 낫겟다 납치.감금만반복반복..이드라마는 가족도없다 연기못하는사람만모엿네</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>## 🔍 VOC 데이터 분석 보고서
+**작성자:** [사내 VOC 데이터 분석가]
+**분석 일시:** 2023. XX. XX
+---
+### 📝 1줄 요약 (Key Takeaway)
+배우들의 연기력 부족과 드라마의 스토리 전개(납치/감금의 반복 등)에 대한 시청자의 극심한 불만과 비난이 포착되었으며, 서비스 품질에 대한 부정적 인식이 매우 높은 수준으로 나타남.
+***
+### 💡 VOC 분석 가이드 (Action Plan)
+본 민원은 단순히 '불편함'의 영역을 넘어, 작품의 **핵심 가치(연기, 서사)**에 대한 근본적인 불만 제기이며, 매우 강한 부정적 감정(분노, 멸시)이 표출된 사례입니다. 향후 재발 방지 및 품질 관리를 위해 다음과 같은 분석 및 조치 가이드를 제안합니다.
+#### 1. 핵심 이슈 도출 (Root Cause Analysis)
+*   **주요 불만 대상:**
+    *   **연기력 (Acting Quality):** 가장 직접적인 비판 지점입니다. 시청자는 연기가 캐릭터나 장면에 몰입하게 만드는 핵심 동력이라고 판단하며, 현재 연기를 '부족하다'고 인식하고 있습니다.
+    *   **서사/전개 (Plot/Pacing):** '납치-감금의 반복'이라는 설정 자체가 지루하거나 클리셰적이라고 판단되어 시청자의 몰입을 방해하고 있습니다.
+    *   **전반적 만족도 (Overall Engagement):** 높은 수준의 분노와 비방적 언어 사용은 작품에 대한 기대치가 높았으나 현재의 결과물이 그 기대치를 크게 밑돌았음을 의미합니다.
+#### 2. 대응 전략 (Guideline)
+| 분류 | 분석 내용 | 제안 조치 (Action Item) |
+| :--- | :--- | :--- |
+| **내부 피드백** | 연기에 대한 강한 불만은 제작진 및 배우에게 즉각 전달되어 향후 작품 기획 시 연출 및 캐스팅 시 품질 관리가 필요함을 시사함. | **[제작팀/콘텐츠팀]** 해당 민원을 참고하여 연기 지도 강화를 검토하고, 대본 검토 단계에서 서사의 반복성(cliché)을 줄일 수 있도록 스토리라인 점검을 요청해야 함. |
+| **위기 관리 (Crisis Management)** | 해당 민원은 감정적 언어가 강하므로, 억압하거나 방어적으로 대응할 경우 2차 논란을 유발할 위험이 높음. | **[운영/CS팀]** 즉각적인 사과나 해명보다는, **'시청자 의견을 수렴하고 있으며 지속적으로 품질 개선을 노력하겠다'**는 방향의 중립적 피드백을 제공하는 것이 바람직함. |
+| **지표 모니터링** | 특정 배우나 설정(이응경, 길용우, 납치 등)에 대한 부정적 언급이 반복되는지 추적해야 함. | **[데이터팀]** 키워드 기반의 감성 분석을 통해 '연기력'과 '배우 이름'의 연관 지표(Negative Association)가 지속적으로 높은지 모니터링하고, 트렌드 변화에 대비해야 함. |
+---
+*(이 요약 및 가이드는 사내 보고용으로 작성되었으며, 감정적인 대응보다는 데이터 기반의 문제 진단과 개선 방향 제시를 목표로 합니다.)*</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>16.35</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1438</v>
+      </c>
+      <c r="G37" t="n">
+        <v>87.95999999999999</v>
+      </c>
+      <c r="H37" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>4회차</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>7</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>울면서 손들고 횡단보도 건널때 뛰쳐나올뻔 이범수 연기 드럽게못해</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>## 📊 VOC 데이터 분석 요약 및 가이드
+**[분석관]** 사내 VOC 데이터 분석가
+---
+### 📝 1줄 요약 (One-Line Summary)
+**[엔터테인먼트/배우 연기]** 특정 배우(이범수)의 과장되거나 비현실적인 연기 표현으로 인해 몰입도가 저하되었다는 부정적 감상 피드백.
+---
+### 📋 분석 가이드 (Analyst's Guide)
+#### 🔍 1. 피드백 분류 (Classification)
+*   **분류 카테고리:** 콘텐츠 품질 (Content Quality) / 예술적 표현 (Artistic Expression)
+*   **감성 점수 (Sentiment):** 매우 부정적 (Highly Negative)
+*   **핵심 키워드:** 연기, 몰입도, 비현실적, 과장, 이범수
+#### 📌 2. 데이터 해석 및 인사이트 (Data Insight)
+1.  **피드백 성격 파악:** 본 민원은 서비스 이용 중 발생한 '불편함'보다는 작품의 '예술적 완성도'에 대한 주관적인 평가 및 비판입니다. 즉, 기술적/물리적 결함(Bug)이 아닌 콘텐츠 자체의 해석 차이입니다.
+2.  **감정적 반응 확인:** 민원인의 감정이 매우 강하고 비난의 수위가 높습니다. 이는 콘텐츠에 대한 기대치와 현재 전달된 내용 간의 괴리가 컸음을 시사합니다.
+3.  **관련 추적 필요성:** 해당 작품의 다른 시청자들의 연기 평가, 스토리 몰입도 피드백을 함께 교차 분석하여 해당 장면/배우에 대한 공통된 의견이 있는지 확인해 볼 필요가 있습니다.
+#### 🛡️ 3. 대응 전략 (Response Strategy)
+**✅ 내부 대응 (Internal Handling):**
+*   **원칙:** 콘텐츠의 예술적 해석은 시청자마다 다름을 인지하고, 해당 의견을 '감상' 차이로 기록 및 분류합니다.
+*   **조치:** 해당 피드백을 제작팀에 전달할 경우, "연출 의도"보다는 "시청자 몰입 저해 요인으로 분석됨"이라는 관점에서 객관적으로 보고해야 합니다. **(방어적 태도는 지양)**
+**✅ 외부 대응 (External Response to Customer):**
+*   **핵심:** 비난의 어투에 감정적으로 반응하지 않고, 의견을 전달해 준 것에 대해 감사함을 표현하는 것이 중요합니다.
+*   **응대 템플릿 (예시):** "시청자님의 솔직하고 강한 의견을 전달해 주셔서 감사합니다. 작품의 연기 표현에 대해 아쉬움을 느끼셨다는 점을 접했으며, 시청자분들마다 작품을 바라보는 관점이 다를 수 있다는 점을 참고하겠습니다." (→ **감사 + 경청 + 중립 유지**)</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1287</v>
+      </c>
+      <c r="G38" t="n">
+        <v>88.47</v>
+      </c>
+      <c r="H38" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>4회차</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>8</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>취향은 존중한다지만 진짜 내생에 극장에서 본 영화중 가장 노잼 노감동임 스토리도 어거지고 감동도 어거지</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>## [사내 VOC 데이터 분석] 민원 요약 및 대응 가이드
+### 🔍 1줄 요약 (핵심 VOC Tag)
+**콘텐츠의 재미(몰입도)와 감동 유발 능력이 현저히 부족하다는 극도의 불만 표출.**
+---
+### 📊 분석 요약 (Data Analysis)
+**1. 감성 분석 (Sentiment):**
+*   **강도:** 매우 부정적 (Very Strong Negative)
+*   **주요 감정:** 실망, 지루함, 불만 (Disappointment, Boredom, Dissatisfaction)
+*   **화자의 태도:** 감정을 직접적으로 배제하기보다, 극도로 높은 기대치 대비 실제 경험의 격차가 크다는 점을 강조하고 있음.
+**2. 핵심 불만 키워드 (Pain Points):**
+*   **핵심 실패 지점:** 재미 (노잼), 감동 (노감동)
+*   **구체적 원인:** 스토리 구성의 문제, 감정선 전달 실패 ('스토리도 어거지', '감동도 어거지' 등)
+*   **잠재적 시사점:** 고객은 단순한 관람을 넘어 '경험'을 기대했으나, 콘텐츠 자체가 기대치를 충족시키지 못함.
+**3. 관련 분류 (Classification):**
+*   **분야:** 콘텐츠 평가 (Content Evaluation) / 서비스 품질 불만 (Quality Complaint)
+---
+### 💡 대응 가이드 (Action Plan)
+**A. 즉각적 대응 (Immediate Response - CS/Service Team):**
+1.  **공감 및 경청:** 고객의 강한 불만(강한 비난)을 수용하며 감정적으로 공감하는 응대가 필수적입니다. (예: "몰입도가 낮았다는 점에 대해 깊이 실망하셨을 고객님의 심정에 공감합니다.")
+2.  **구체적 피드백 수집:** 단순 '노잼'을 넘어, 스토리가 지루해지기 시작한 구체적인 시점이나 캐릭터에 대한 불만 등 추가적인 피드백을 정중히 요청합니다. (향후 개선을 위한 정성적 데이터 확보)
+3.  **만족도 회복(Service Recovery):** 상황에 따라 재관람권 또는 소정의 적립금 등 보상안을 제시하여 부정적인 경험을 중립 또는 긍정적인 경험으로 전환을 유도합니다.
+**B. 내부 품질 관리 (Internal Quality Control - Creative/Curation Team):**
+1.  **표준 재점검 (Review):** 해당 콘텐츠(영화/전시 등)의 기획 단계부터 최종 검수 단계까지, '몰입도'와 '감동 유발 지점'에 대한 내부 리뷰 기준(Checklist)을 재설정하고 점검합니다.
+2.  **콘텐츠 밸런스 강화:** 스토리의 구조적 결함(Plot Hole, Pacing 등)을 분석하고, 고객이 기대하는 감정적 카타르시스를 제공할 수 있도록 콘텐츠의 서사적 밀도를 높이는 방안을 고려합니다.
+**C. 중장기 전략 (Long-term Strategy - Product Planning):**
+1.  **취향 다양성 포용:** "취향 존중"이라는 문구와 극단적인 불만이 공존하므로, 극단적인 호불호가 갈리는 콘텐츠를 대규모로 제공하기보다는, 기본적인 완성도(스토리, 연출)가 보장된 콘텐츠를 선별하여 제공하는 큐레이션 전략을 강화할 필요가 있습니다.
+2.  **체험 가치 제고:** 단순 콘텐츠 시청을 넘어, 공간적 경험(음향, 환경 등)이나 부가적인 서비스를 통해 '재미'와 '감동'이 아닌 다른 가치(프리미엄 경험)로 만족도를 높이는 대안을 모색합니다.</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>18.32</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1606</v>
+      </c>
+      <c r="G39" t="n">
+        <v>87.66</v>
+      </c>
+      <c r="H39" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>4회차</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>9</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>굿바이 레닌 표절인것은 이해하는데 왜 뒤로 갈수록 재미없어지냐</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>## 📊 사내 VOC 데이터 분석 보고서
+**🔍 VOC 요약 (1줄)**
+콘텐츠의 후반부 전개 과정에서 몰입도 및 재미가 하락하는 '후반부 피로감(Burn-out)'에 대한 부정적 피드백입니다.
+---
+### 📋 분석 및 가이드
+**🔍 핵심 키워드 분석**
+*   **Issue:** 후반부 몰입도 저하 (Pacing/Drop-off)
+*   **Sentiment:** 실망, 기대치 미달
+*   **Context:** 표절 의식은 인정하나, 자체적인 흥미 유발 장치가 부족하다고 판단함. (단순한 '표절' 지적보다는 '자체적 완성도' 지적에 초점)
+**💡 콘텐츠 기획 및 제작 가이드 (Action Plan)**
+이와 같은 후반부 몰입도 저하 피드백은 콘텐츠의 중반부 설계 및 후반부 클라이맥스 구성에 문제가 있음을 시사합니다. 아래 가이드라인을 바탕으로 콘텐츠 품질을 일관성 있게 유지할 것을 권장합니다.
+**✅ 1. 페이싱(Pacing) 설계 점검 및 강화**
+*   **중반부 동력 유지:** 초반에 확보한 흥미와 몰입도가 중반부에 급격히 소모되거나 늘어지지 않도록 사건의 발생 주기(Event Cycle)를 재검토해야 합니다.
+*   **완급 조절:** 모든 에피소드가 동일한 강도를 유지하기보다, 후반부로 갈수록 긴장감을 고조시키거나 예상치 못한 반전을 통해 독자의 집중력을 지속적으로 자극해야 합니다.
+**✅ 2. 서사적 일관성(Narrative Consistency) 확보**
+*   **주제 명확화:** 초기 설정된 핵심 주제나 갈등이 후반부에 흐릿해지거나 산만해지지 않도록 유지해야 합니다.
+*   **개연성 점검:** 후반부 캐릭터의 행동이나 사건의 전개가 갑자기 비논리적이거나(OOC, Out of Character) 급진적으로 느껴지는 지점이 없는지 면밀히 검토해야 합니다.
+**✅ 3. 클라이맥스(Climax)의 강력한 보장**
+*   **기대치 충족:** 초반부에 던진 모든 미끼(Hook)와 갈등이 후반부의 최종 결과에서 해소되거나 더 큰 의미를 지니도록 설계해야 합니다. 후반부가 단순히 늘어지는 '풀어헤치기'가 아닌, 강력한 '보상(Reward)'을 제공해야 합니다.
+**✅ 4. 제작 단계에서의 피드백 루프 도입**
+*   **독자 테스트 강화:** 콘텐츠 완성 후 시청자/독자 테스트를 진행할 때, 특히 **후반부(예: 중반 이후부터 마지막 25%)** 구간에서 몰입도 저하 지점을 포착하는 설문 문항을 강화해야 합니다.</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>15.34</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1351</v>
+      </c>
+      <c r="G40" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="H40" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>4회차</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>10</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>재미없다 지루하고. 같은 음식 영화인데도 바베트의 만찬하고 넘 차이남....바베트의 만찬은 이야기도 있고 음식 보는재미도 있는데 ; 이건 볼게없다 음식도 별로 안나오고, 핀란드 풍경이라도 구경할랫는데 그것도 별로 안나옴 ㅡㅡ</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>## 🔍 VOC 데이터 분석 보고서
+**작성자:** 사내 VOC 데이터 분석가
+**분석 일자:** 2023.XX.XX
+**원문 민원:** "재미없다 지루하고. 같은 음식 영화인데도 바베트의 만찬하고 넘 차이남....바베트의 만찬은 이야기도 있고 음식 보는재미도 있는데 ; 이건 볼게없다 음식도 별로 안나오고, 핀란드 풍경이라도 구경할랫는데 그것도 별로 안나옴 ㅡㅡ"
+---
+### 📝 1줄 요약 (One-Line Summary)
+**[콘텐츠 품질/몰입도 저하]** 핵심 경쟁 요소인 서사(Storytelling) 및 시각적 매력(Food/Scenery)이 부족하여, 기대 수준(Reference Title: 바베트의 만찬)에 미치지 못하고 지루함을 유발함.
+---
+### 🧭 대응 전략 가이드 (Action Plan &amp; Guideline)
+이번 민원은 단순한 '재미 없음'을 넘어, 특정 장르(음식/풍경 콘텐츠)에서 소비자가 기대하는 **최소한의 시각적/내용적 기준(Baseline)**이 충족되지 않았음을 시사합니다.
+**1. 🎯 핵심 Pain Point 분석**
+*   **Pain Point 1: 서사/내용 부족 (Narrative Void)**
+    *   단순한 영상 나열이 아닌, 시청자가 감정적으로 몰입할 수 있는 **'이야기'**의 부재가 지루함의 주원인입니다.
+*   **Pain Point 2: 시각적 매력 격차 (Visual Appeal Gap)**
+    *   음식 콘텐츠의 핵심 가치인 **'Food Porn'** 요소(음식의 비주얼, 조리 과정의 미학)와 **'Setting'** 요소(핀란드 풍경 등 공간의 매력)의 질이 경쟁 콘텐츠 대비 현저히 낮습니다.
+*   **Pain Point 3: 기대치 미충족 (Expectation Mismatch)**
+    *   소비자는 성공적인 벤치마크 콘텐츠(바베트의 만찬 등)를 기준으로 기대를 형성하고 있으며, 현재 콘텐츠는 이 기준에 도달하지 못했습니다.
+**2. 🛠 제안 조치 사항 (Actionable Recommendations)**
+| 분야 | 세부 조치 (Action) | 목표 (Goal) |
+| :--- | :--- | :--- |
+| **[콘텐츠 기획]** | **서사 구조 강화 (Script Review)** | 음식/풍경을 보여주는 '장면'이 아닌, 그 음식과 장소에 얽힌 '이야기'를 삽입하여 몰입도를 높여야 합니다. (예: 특정 음식의 역사, 레시피의 의미 등) |
+| **[제작/기술]** | **시각적 품질 업그레이드 (Production Upgrade)** | 음식 촬영 및 조명, 미장센(Mise-en-scène)의 완성도를 재검토하고, 음식의 질감을 극대화하는 촬영 기법을 적용해야 합니다. |
+| **[마케팅/경쟁 분석]** | **차별화 포인트 재정립 (Competitive Benchmarking)** | 성공한 경쟁 콘텐츠(바베트의 만찬 등)의 **'성공 요소'**를 세부적으로 분석(스크립트, 연출, 음악, 편집 속도 등)하고, 당사 콘텐츠의 미흡한 부분을 갭(Gap) 분석하여 보완 전략을 수립합니다. |
+| **[UX/UX]** | **후반 작업 보완 (Post-Production Polish)** | 지루함은 편집 리듬에서도 발생할 수 있습니다. 영상의 페이싱(Pacing)과 배경음악/효과음을 검토하여 역동성을 확보해야 합니다. |</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1551</v>
+      </c>
+      <c r="G41" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="H41" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>5회차</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B42" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>아 더빙.. 진짜 짜증나네요 목소리</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>사내 VOC 데이터 분석가로서 민원에 대한 분석 요약 및 후속 조치 가이드를 다음과 같이 제출합니다.
----
-### 🔍 VOC 분석 리포트
-**1. 민원 요약 (One-Line Summary)**
-&gt; **[더빙/콘텐츠]** 더빙 내 목소리 톤 또는 연기 품질에 대한 불만 및 부정적인 감정 표출.
-**2. 분석 및 진단 (Analysis &amp; Diagnosis)**
-*   **키워드:** 더빙, 목소리, 짜증
-*   **문제 유형:** 콘텐츠 현지화 및 제작 품질(Localization/Production Quality).
-*   **핵심 이슈:** 사용자가 콘텐츠의 '음성적 요소'를 불쾌하게 느끼고 있으며, 이는 몰입도 저하의 직접적인 원인이 됨. 단순한 취향 문제가 아닌, 전달력이나 품질 기준에 대한 의문일 수 있음.
-**3. 대응 및 후속 조치 가이드 (Action Plan)**
-| 구분 | 내용 | 담당 부서 | 목표 |
-| :--- | :--- | :--- | :--- |
-| **💡 즉각 대응 (Short-Term)** | **피드백 세분화 및 데이터 수집:** 해당 민원을 제기한 이용자에게 구체적으로 '어떤 점(톤, 발음, 감정 전달 등)'이 불쾌했는지 추가 피드백을 요청하여 데이터 정성 분석(Qualitative Data)을 진행한다. | CS/콘텐츠 팀 | 문제의 원인(Root Cause) 구체화. |
-| **⚙️ 품질 점검 (Mid-Term)** | **더빙 가이드 재점검:** 현재 사용된 더빙 아티스트의 연기 지침(Tone/Style Guide)이 사전에 충분히 전달되었는지, 혹은 프로젝트의 톤앤매너에 적합한지 검토한다. | 제작/Localization 팀 | 더빙 표준 품질 기준 확립 및 준수 여부 확인. |
-| **🚀 개선 방안 (Long-Term)** | **테스트 및 교체 검토:** 만약 피드백이 반복되거나 광범위하다면, 해당 대사의 재녹음(Re-dubbing) 또는 다른 성우/더빙 버전으로 대체하는 방안을 검토한다. | 제작/콘텐츠 팀 | 이용자 만족도를 높일 수 있는 최적의 음향 요소 제공. |
-**📌 요약 가이드: 이 민원은 '단순 불만'이 아닌 '콘텐츠 품질 문제'로 간주하고, 음향 요소에 대한 정량적/정성적 검토를 시작해야 합니다.**</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>14.25</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1167</v>
-      </c>
-      <c r="G6" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="H6" t="n">
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>**🔍 VOC 요약 및 분석 결과**
+**✅ 1줄 요약 (Summary)**
+더빙(Voice Acting)의 목소리 톤/품질에 대한 사용자의 불만이 매우 강하며, 이에 대해 짜증과 불쾌감을 표현함.
+**💡 분석 가이드 (Action/Insight)**
+1. **카테고리 분류:** 콘텐츠 품질(Audio/Voice) 관련 민원으로 분류.
+2. **업무 담당 부서:** 콘텐츠 기획팀 및 더빙(성우) 담당 팀으로 즉시 이관 필요.
+3. **후속 조치 제안:** 해당 더빙에 대한 음원 품질 검토(A/S) 진행 및 사용자가 언급한 특정 목소리의 문제 여부 확인이 필요하며, 향후 콘텐츠 제작 시 성우 섭외 가이드 및 녹음 환경 표준 마련을 위한 피드백으로 활용해야 함.
+4. **감성 분석:** '짜증나네요'라는 표현을 통해 감성 점수(Sentiment Score)가 매우 낮음(Negative, Strong)을 확인함.</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="F42" t="n">
+        <v>502</v>
+      </c>
+      <c r="G42" t="n">
+        <v>87.58</v>
+      </c>
+      <c r="H42" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>5회차</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>너무재밓었다그래서보는것을추천한다</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>## [사내 VOC 분석 보고서]
+**📋 분석 대상:** 민원/피드백 데이터
+**👤 분석가:** VOC 데이터 분석팀
+---
+### 📝 1줄 요약 (Executive Summary)
+제품의 **극찬(Taste Satisfaction)**과 이에 따른 **적극적인 구매 및 사용 추천 의향**이 확인된 매우 긍정적인 피드백입니다.
+---
+### 🔎 VOC 분석 및 대응 가이드 (Action Guideline)
+본 피드백은 단순 민원이 아닌, **브랜드 자산(Brand Asset)**으로 활용해야 할 매우 가치 있는 긍정 데이터입니다. 문제 해결(Troubleshooting)이 아닌, 성공 사례 활용(Leveraging) 관점에서 가이드를 제시합니다.
+#### 1. 데이터 분류 및 태깅 (Classification &amp; Tagging)
+| 항목 | 분류 | 세부 태그 |
+| :--- | :--- | :--- |
+| **감성 분석** | Positive (긍정) | 만족, 극찬, 추천 |
+| **주요 이슈** | 품질/Taste | 맛(Flavor), 품질 만족도 |
+| **피드백 유형** | 추천 (Promotion) | 입소문, 재구매 의사 높음 |
+#### 2. 내부 조치 사항 (Internal Action Plan)
+*   **🔥 데이터 아카이빙:** 해당 피드백을 '최고 만족 사례'로 분류하여 DB에 등록하고, 향후 마케팅 및 품질 관리(QA) 기준 데이터로 활용합니다.
+*   **✨ 품질 유지 확인:** 현재의 높은 만족도가 일시적인 현상이 아닌지, 제조/운영 프로세스에서 품질 기준이 흔들리지 않는지 재점검합니다. (가장 중요)
+*   **📣 마케팅 자료 활용 검토:** 고객의 자발적인 추천은 가장 강력한 마케팅입니다. (개인정보 보호 범위 내) 해당 후기를 검토하여 마케팅 채널에 활용할 수 있는지 검토합니다.
+#### 3. 종합 의견 (Analyst's Conclusion)
+해당 피드백은 **현재 제품이 시장에서 매우 높은 만족도를 확보하고 있음**을 입증하는 명확한 지표입니다. 품질 관리에 집중하여 이러한 긍정적 경험이 모든 고객에게 균일하게 제공되도록 관리하는 것이 현재의 최우선 과제입니다.</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1109</v>
+      </c>
+      <c r="G43" t="n">
+        <v>87.61</v>
+      </c>
+      <c r="H43" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>5회차</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>3</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>교도소 이야기구먼 ..솔직히 재미는 없다..평점 조정</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>## [VOC 분석 보고]
+**분석 담당자:** VOC 데이터 분석팀
+**작성일:** YYYY. MM. DD.
+---
+### 📝 1줄 요약 (Summary)
+제공되는 콘텐츠 주제(교도소 관련)의 흥미 및 재미가 부족하다는 불만과 해당 콘텐츠에 대한 부정적 평가를 바탕으로 평점 조정을 요구함.
+### 🔎 상세 분석 및 가이드 (Analysis &amp; Guideline)
+**1. 핵심 키워드 및 분류**
+*   **핵심 키워드:** 교도소, 재미 없음, 평점 조정
+*   **VOC 분류:** 콘텐츠 품질 및 테마 불만 (Content Quality / Theme Dissatisfaction)
+*   **감성:** 부정 (Negative)
+*   **요구 사항:** 평가 변경 (Rating Adjustment), 콘텐츠 개선 (Content Improvement)
+**2. 문제 진단 (Insight)**
+*   **Pain Point:** 특정 콘텐츠 주제(교도소 관련 이야기)가 고객의 흥미(Engagement)를 유발하는 데 실패했거나, 내용 구성 자체가 너무 무겁고 지루하다고 판단됨.
+*   **Root Cause (가정):** 콘텐츠 테마의 지나친 편중 혹은 독자의 기대치와 다르게 진지하고 어둡게 다루어졌을 가능성.
+**3. 액션 플랜 (Guideline to Content/Product Team)**
+| 구분 | 실행 목표 | 세부 조치 사항 | 담당 부서 | 기한 |
+| :--- | :--- | :--- | :--- | :--- |
+| **[단기 대응]** | **불만 해소 및 데이터 확보** | 해당 콘텐츠에 대한 고객의 부정적 피드백을 추가 수집하고, 다른 유사 주제 콘텐츠의 만족도와 비교 분석하여 문제의 심각성을 객관화할 것. | CS / 데이터 분석 | 1주일 이내 |
+| **[중기 개선]** | **콘텐츠 다양성 강화** | 교도소와 같이 특정 사회적/무거운 테마의 콘텐츠 비율을 재검토하고, 고객들이 선호할 만한 **경량화(Lightening)** 또는 **대체 테마**를 발굴하여 콘텐츠 라이브러리에 반영할 것. | 콘텐츠 기획팀 | 차기 업데이트 시 |
+| **[장기 전략]** | **테마 적정성 검토** | 고객의 전체 세그먼트(Age, Interest)별 선호 테마 데이터를 확보하여, 특정 테마가 전체 사용자에게 편향적인 만족도를 주기보다는 다양한 관심을 충족시킬 수 있도록 콘텐츠 전략을 재수립할 것. | 제품 전략팀 | 분기 단위 검토 |</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1295</v>
+      </c>
+      <c r="G44" t="n">
+        <v>88.01000000000001</v>
+      </c>
+      <c r="H44" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>5회차</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>4</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>막 걸음마 뗀 3세부터 초등학교 1학년생인 8살용영화.ㅋㅋㅋ...별반개도 아까움.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>## 📊 VOC 분석 보고 (내부용)
+**분석가:** 사내 VOC 데이터 분석팀
+**VOC 등록일:** [작성일]
+**분류:** 콘텐츠 만족도 저하 (아동/가족)
+---
+### 📄 1줄 요약 (Summary)
+**아동 대상 영화(3~8세)의 콘텐츠 완성도 및 만족도에 대한 극도로 낮은 평가 접수.**
+---
+### 🛠️ 분석 가이드 및 후속 조치 (Action Plan)
+본 VOC는 단순한 불만을 넘어, 특정 타겟층(어린이 및 학부모)의 콘텐츠 가치 인식 자체가 매우 낮음을 시사합니다. 단순 리뷰에 머무르지 않고, **콘텐츠의 실질적인 매력과 시장 적합성**을 다각도로 검증해야 합니다.
+#### 🔎 1단계: VOC 정량/정성 분석 (Diagnostic Phase)
+*   **키워드 추출:** '별반개도 아까움', '3세', '8살' 등 연령 및 가치와 관련된 부정적 표현을 추출하고, 유사 VOC가 추가로 발생하는지 트래킹합니다.
+*   **정성 심층 분석:** 해당 이용자가 어떤 지점에서 가치를 느끼지 못했는지 (스토리, 영상미, 캐릭터 매력, 교육적 요소 등)를 파악하기 위해 다른 유사 리뷰를 교차 분석합니다.
+*   **데이터 비교:** 해당 콘텐츠의 타 연령대 (예: 10~15세) 리뷰와 3~8세 리뷰의 만족도 격차를 분석하여 문제의 집중도를 확인합니다.
+#### 🎯 2단계: 원인 파악 (Root Cause Analysis)
+*   **타겟 적합성 검토:** 현재 콘텐츠가 '3세부터 8세'의 발달 단계 및 흥미 영역을 충분히 반영하고 있는지 제작 가이드라인과 비교 검토합니다. (ex. 너무 복잡함/너무 단순함/교훈 전달이 지루함)
+*   **경쟁사 벤치마킹:** 동 연령층을 타겟으로 하는 경쟁사 아동 콘텐츠의 성공 요소를 분석하고, 본 콘텐츠가 비교 대비 어떤 부분에서 경쟁력을 잃었는지 비교합니다.
+*   **콘텐츠 품질 검수:** 제작 단계에서의 피드백 누락 가능성이 있는지, 콘텐츠 자체의 후반 검수 과정에 문제가 없었는지 프로세스를 점검합니다.
+#### 💡 3단계: 실행 방안 (Recommendation)
+*   **단기 대응 (Short-term):** 고객 CS 팀에 해당 의견을 전달하고, 콘텐츠에 대한 개선 포인트를 정리하여 재접수 시 활용할 수 있도록 가이드라인을 제공합니다. (예: "어떤 요소가 부족했는지 알려주세요.")
+*   **장기 대응 (Long-term):** 향후 아동/가족 콘텐츠 기획 시, **'연령별 발달 단계 기반의 매력도 테스트'**를 의무화하고, 실제 타겟층의 선행 테스트 비율을 높이는 정책을 제안합니다.</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1354</v>
+      </c>
+      <c r="G45" t="n">
+        <v>86.54000000000001</v>
+      </c>
+      <c r="H45" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>5회차</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>원작의 긴장감을 제대로 살려내지못했다.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>네, VOC 데이터 분석가로서 해당 피드백을 분석하고 실행 가능한 가이드를 정리해 드리겠습니다.
+---
+### 📊 **VOC 분석 결과 보고**
+**🔍 1. 핵심 요약 (One-Sentence Summary)**
+원작이 지닌 고유의 긴장감 및 서사적 몰입도가 콘텐츠 전반의 연출 및 구현 과정에서 충분히 전달되지 못했다는 의견입니다.
+**💡 2. 분석 가이드 및 대응 방안 (Actionable Guidance)**
+이 피드백은 단순히 '개선 요구'를 넘어, **원작 IP의 핵심 가치(Core Value)**가 고객 경험 단계에서 손실되고 있음을 의미합니다. 단순한 품질 문제가 아닌, 기획 및 제작 단계의 근본적인 검토가 필요합니다.
+#### **✅ [내부 액션 플랜] 당장 검토해야 할 3가지**
+**1. [기획/콘텐츠 팀] 원작 분석 및 디테일 재점검 (Root Cause Analysis)**
+*   **진단:** 원작의 '긴장감'이 어떤 요소(빠른 호흡, 미묘한 사운드, 캐릭터의 심리적 압박, 클리프행 등)에서 기인하는지 원문을 면밀히 분석해야 합니다.
+*   **액션:** 현재 제작물에서 원작의 긴장 요소를 의도적으로 **'강화'하거나 '반영'**하지 못한 지점(Pacing, Narrative Arc 등)을 스크립트와 비교하여 찾아야 합니다.
+**2. [제작/연출 팀] 감각적 연출 강화 (Execution Focus)**
+*   **진단:** 긴장감은 시각적 요소뿐만 아니라 청각적, 리듬적 요소에 크게 좌우됩니다.
+*   **액션:**
+    *   **사운드 디자인:** 적절한 긴장감을 줄 수 있는 미니멀하거나 역동적인 사운드(BGM, 효과음)의 배치가 누락되거나 약한지 재검토합니다.
+    *   **페이싱(Pacing):** 중요한 순간에 의도적으로 호흡을 조절하거나 긴장을 고조시키는 연출(Slow Motion, 클로즈업 등)을 강화할 필요가 있습니다.
+**3. [QA/피드백 반영] '감성 필터'를 통한 테스트 (Post-Production Check)**
+*   **진단:** 완성된 결과물에 대해 외부 전문가나 원작 팬을 대상으로 단순 완성도 검토를 넘어 **'몰입감 및 감정 이입도'**를 평가하는 검증 단계를 추가해야 합니다.
+*   **액션:** 시청자 그룹을 나누어 "원작과 비교했을 때 긴장감이 느껴지는 지점을 지적해 달라"는 구체적인 가이드라인을 제시하며 리액션을 체크하는 테스트를 의무화합니다.</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1224</v>
+      </c>
+      <c r="G46" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="H46" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>5회차</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>6</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>별 반개도 아깝다 욕나온다 이응경 길용우 연기생활이몇년인지..정말 발로해도 그것보단 낫겟다 납치.감금만반복반복..이드라마는 가족도없다 연기못하는사람만모엿네</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>## 📊 VOC 데이터 분석 보고서 (Internal)
+**[분석 담당자: 사내 데이터 분석가]**
+### 📌 1줄 핵심 요약 (One-Line Summary)
+**[연기 및 서사 비판]** 특정 배우들의 연기력 부족 및 극의 반복적이고 단조로운 서사 전개(납치/감금 클리셰 반복)에 대한 시청자의 매우 강하고 부정적인 불만 제기.
+***
+### 💡 VOC 대응 및 개선 가이드 (Guidance &amp; Action Plan)
+본 민원은 단순한 개인적 취향을 넘어, 작품의 **핵심 구성 요소(연기력, 서사 밀도)**에 대한 구조적인 비판을 담고 있습니다.
+**1. 🚨 즉각 대응 방안 (Crisis Management)**
+*   **반박 지양 및 공감 유도:** 감정적인 공격(욕설, 비난)에 직접적으로 대응하기보다, 시청자의 '작품의 지루함'과 '연출의 아쉬움'에 대해 경청하는 형식으로 피드백을 수렴해야 합니다. (예: "시청자분께서 작품의 전개나 연기 구성에 아쉬움을 느끼셨다는 점을 저희도 인지하고 있습니다.")
+*   **데이터 축적:** 해당 민원을 주요 키워드(연기, 지루함, 클리셰, 서사 부재)와 연계하여 다른 부정적 VOC와 그룹화하고, 콘텐츠 기획 시 위험 요인으로 분류합니다.
+**2. 🛠 중장기 개선 제언 (Content Improvement)**
+*   **서사 다양성 강화 (Plot):** 반복적인 위기 상황(납치/감금)이나 예측 가능한 플롯 구조에 대한 시청자의 피로도가 높습니다. 향후 콘텐츠 기획 단계에서 사건의 고유성(Uniqueness)을 확보하고, 인물 간의 깊은 내적 갈등과 관계 변화를 중심으로 서사를 구축할 필요가 있습니다.
+*   **배우 캐스팅 및 연기 디렉팅 (Casting &amp; Acting):** 특정 배역에 대해 연기 역량에 대한 강한 비판이 집중되었습니다. 캐스팅 단계에서 해당 역할의 요구되는 연기 스펙과 배우의 역량 간의 적합성(Fit)을 재점검하고, 현장에서는 배우들이 인물의 감정선을 명확히 표현할 수 있도록 심도 있는 디렉팅 및 코칭을 제공해야 합니다.
+*   **톤앤매너 검토 (Tone &amp; Manner):** "가족도 없다", "연기 못하는 사람만 모였다"는 식의 비하적인 평가는 작품의 정서적 연결고리(Emotional Resonance)가 부족하다는 방증입니다. 극의 주제가 전달하는 감정적 밀도가 시청자에게 충분히 와닿지 않고 있음을 시사하며, 이를 보완할 요소(예: 관계 변화, 공통의 가치)를 재검토해야 합니다.</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>16.73</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1466</v>
+      </c>
+      <c r="G47" t="n">
+        <v>87.62</v>
+      </c>
+      <c r="H47" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>5회차</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>7</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>울면서 손들고 횡단보도 건널때 뛰쳐나올뻔 이범수 연기 드럽게못해</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>## 🔍 VOC 분석 결과 보고
+### 📄 1줄 요약 (Summary)
+**배우 이범수의 특정 장면(횡단보도 연기)에서 표현력 및 몰입도가 부족하다는 강한 부정적 피드백이 접수됨.**
+---
+### 📝 가이드라인 및 조치 방안 (Action Plan)
+본 민원은 시청자 경험(UX) 중 **콘텐츠의 완성도 및 배우의 연기 퀄리티**에 대한 비판으로 분류됩니다. 해당 이슈를 처리하기 위해 다음과 같은 단계의 내부 가이드를 제안합니다.
+**1. \[분석 및 분류 단계] (Analysis &amp; Classification)**
+*   **클레임 분류:** 콘텐츠 품질 (Content Quality) / 연출 및 연기력 (Acting &amp; Direction)
+*   **심각도 평가:** (Rating: High) - 관람객이 '놀랐다', '못하겠다'와 같은 강한 감정 표현을 사용한 것으로 보아 단순 선호도 문제가 아닌, 장면의 완성도에 대한 지적입니다.
+*   **핵심 키워드 추출:** 이범수, 연기, 횡단보도, 몰입도, 오버액션/부족.
+**2. \[내부 검토 및 확인 단계] (Internal Review &amp; Verification)**
+*   **담당 부서 협의:** 콘텐츠 제작팀(연출/작품부)에 해당 VOC를 전달하여 피드백의 정확한 맥락을 확인해야 합니다.
+*   **내부 재검토:** 해당 장면의 연기 의도(Director's Intent)가 명확하게 전달되었는지, 혹은 배우의 감정 표현이 과도하게 느껴졌는지 내부적으로 재검토합니다.
+*   **정량화 필요:** '드럽게 못한다'와 같은 정성적 표현을 실제 시청자들이 몰입을 방해한다고 느낀 지점(예: 과한 연기, 디테일 부족 등)으로 구체화하여 평가해야 합니다.
+**3. \[후속 조치 방향] (Recommendation &amp; Action)**
+*   **단기적 대응 (Immediate Action):** 해당 피드백을 제작진에게 전달하여 향후 촬영 또는 편집 단계에서 해당 장면의 연기 디렉션에 대한 검토가 이루어지도록 리마인드합니다.
+*   **장기적 대응 (Long-term Improvement):** 만약 이 VOC가 시리즈 전체의 연기 톤에 대한 일환으로 나온 것이라면, 향후 배우 캐스팅 시 해당 캐릭터에 적합한 연기 톤을 재확인하거나, 연기 코칭 시스템을 강화하는 방안을 검토해야 합니다.
+**📌 요약하자면, 본 VOC는 콘텐츠의 크리에이티브 품질 문제이므로, 단순 CS 응대가 아닌 제작팀과의 협업을 통해 개선 포인트를 도출해야 합니다.**</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1473</v>
+      </c>
+      <c r="G48" t="n">
+        <v>87.33</v>
+      </c>
+      <c r="H48" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>5회차</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>8</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>취향은 존중한다지만 진짜 내생에 극장에서 본 영화중 가장 노잼 노감동임 스토리도 어거지고 감동도 어거지</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>## 🔍 VOC 분석 결과 보고
+**분석자:** 사내 VOC 데이터 분석가
+**분석 목적:** 고객 민원 요약 및 후속 조치 가이드 제시
+***
+### 📝 1줄 요약
+**[콘텐츠 품질 불만] 해당 영화의 스토리 전개 및 감동 요소가 현저히 부족하여 극장에서 본 작품 중 최하의 만족감을 표함.**
+***
+### 🧭 가이드라인 (후속 조치 및 분석 방향)
+이 민원은 서비스 자체의 문제(상영 환경, 응대 등)가 아닌 **'콘텐츠 자체의 질(영화의 연출, 서사 등)'**에 대한 직접적인 평가이므로, 다음과 같은 내부 절차를 따를 것을 권고합니다.
+#### 1. 분류 및 태깅 (Classification &amp; Tagging)
+*   **분류:** 콘텐츠 만족도 저하 (Content Satisfaction Drop)
+*   **태그:** \#스토리부족, \#감동없음, \#재미없음, \#작품평
+#### 2. 심층 분석 (Deep Dive Analysis)
+*   **경향성 확인:** 해당 작품에 대한 다른 고객들의 리뷰를 크롤링하여 이 민원이 **'일회성 극단적 개인 취향'**인지, 아니면 **'작품 전반의 평가 하향 추세'**인지를 확인해야 합니다.
+*   **메타데이터 연동:** 이 민원을 해당 작품의 상영 정보, 평점 데이터, 평점 분포 그래프와 연동하여 '부정적 감성 키워드' 발생 시의 일반적인 만족도 변화를 추적합니다.
+#### 3. 대응 전략 (Action Plan)
+*   **단기 대응 (CS):** 고객에게 정중히 경청했음을 알리고, (필요시) '다른 장르/작품 추천' 등의 우회적 만족도 회복 시도를 검토합니다. (단, 작품 자체의 품질 논란에 대해 반박하거나 변명하지 않도록 주의)
+*   **중장기 대응 (Content Feedback Loop):** 이 민원을 **'콘텐츠 기획/제작팀 또는 콘텐츠 공급사(배급사)에 정량적 피드백으로 전달'**해야 합니다. 고객의 '노잼/노감동'이라는 서사적 불만이 곧 다음 작품 기획 시 참고해야 할 핵심 VOC가 됩니다.
+**➡️ 결론:** 해당 민원은 **'감성적 평가'**이므로, 운영팀의 대응보다는 **'분석 데이터를 통한 콘텐츠 품질 개선 요청'**의 목적으로 활용하는 것이 가장 적절합니다.</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1175</v>
+      </c>
+      <c r="G49" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="H49" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>5회차</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>9</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>굿바이 레닌 표절인것은 이해하는데 왜 뒤로 갈수록 재미없어지냐</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>## 📢 VOC 분석 결과 및 대응 가이드
+**분석 역할:** 사내 VOC 데이터 분석가
+---
+### 📝 1. 민원 1줄 요약 (One-Sentence Summary)
+**콘텐츠의 원작 유사성(표절)은 인지하고 있으나, 서사 전개 과정에서 중후반부의 몰입도가 급격히 저하되는 문제(Pacing 및 Sustained Engagement)에 대해 불만을 제기함.**
+---
+### 💡 2. 핵심 인사이트 및 가이드 (Actionable Guide)
+이 민원은 단순한 불만을 넘어, 콘텐츠의 **'지속 가능성(Sustain)'** 및 **'서사 구조의 완성도'**에 대한 핵심적인 지적입니다. 시청자는 초반의 흥미 유발 요소(원작 유사성 또는 초반 설정)는 인정하지만, 그 이후 플롯이 정체되거나 에너지를 잃는 지점에서 이탈 위협을 느끼고 있습니다.
+#### **🔍 분석 포인트 (Diagnosis)**
+*   **Pacing 저하:** 이야기의 전개 속도가 후반부로 갈수록 느려지거나, 에너지를 잃고 정체되고 있다고 판단합니다.
+*   **차별점 부재:** 원작에 대한 지식(혹은 표절 인정)은 시청자에게 인지되고 있습니다. 후반부로 갈수록 **'왜 이 이야기를 계속 봐야 하는가?'**에 대한 새로운 동기 부여나 긴장감이 부족할 수 있습니다.
+*   **갈등 구조 해소 방식:** 갈등이 너무 쉽게 해소되거나, 혹은 해소될 기회 없이 늘 같은 수순으로 진행될 때 재미가 반감됩니다.
+#### **✅ 개선 가이드 (Action Plan)**
+**1. [콘텐츠 제작팀 대상] 서사 구조(Plot) 보강 요청 (장기 관점)**
+    *   **Midpoint Shift 강화:** 이야기의 중반 지점(Midpoint)에서 예측 가능한 전개를 깨는 '변수'나 '급격한 변화'를 도입하여 시청자의 기대감을 최고점으로 끌어올려야 합니다.
+    *   **갈등의 난이도 상승:** 후반부로 갈수록 외부 환경이나 내부적 갈등의 난이도를 점진적으로 상승시켜, 해결 자체가 큰 노력을 요하게 만들어야 긴장감이 유지됩니다.
+    *   **'Why'의 심화:** 단순히 사건이 터지는 것을 넘어, 캐릭터가 이 상황에서 왜 고통받고(Why), 어떤 선택을 해야 하는가에 대한 심리적 깊이를 추가해야 합니다.
+**2. [마케팅/PR팀 대상] 인식 관리 및 소통 (단기 관점)**
+    *   **기대치 관리:** 콘텐츠의 '원작 오마주'적 성격에 대해서는 명확히 인정하되, **'우리가 새롭게 구축한 독창적인 매력'**에 대해 적극적으로 홍보하여 시청자에게 새로운 시각을 제공해야 합니다.
+    *   **피드백 반영:** 해당 민원을 '후반부 전개 보강 필요'로 분류하고, 추후 관련 콘텐츠 기획 시 **'지속 가능한 몰입도'**를 핵심 지표로 활용하여 가이드라인에 반영해야 합니다.</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1438</v>
+      </c>
+      <c r="G50" t="n">
+        <v>86.78</v>
+      </c>
+      <c r="H50" t="n">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>5회차</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>10</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>재미없다 지루하고. 같은 음식 영화인데도 바베트의 만찬하고 넘 차이남....바베트의 만찬은 이야기도 있고 음식 보는재미도 있는데 ; 이건 볼게없다 음식도 별로 안나오고, 핀란드 풍경이라도 구경할랫는데 그것도 별로 안나옴 ㅡㅡ</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>**[사내 VOC 데이터 분석 보고]**
+**1. 1줄 요약 (Summary)**
+내용의 몰입도와 시각적 만족도가 매우 낮으며, 음식 및 풍경 등 기대했던 영상적 요소가 부족하여 흥미를 느끼지 못한다는 의견임.
+**2. 분석 가이드 (Actionable Guide)**
+**[요약 및 핵심 문제 진단]**
+*   **핵심 불만:** 지루함, 볼거리 부족 (시각적/내러티브적 빈곤)
+*   **주요 지적 사항:** 1. 음식 비주얼 부재 (예술적 연출 요구), 2. 풍경 (핀란드)의 매력 전달 실패
+*   **참조점:** 레퍼런스 작품(바베트의 만찬)을 통해 기대했던 '미각적 즐거움'과 '이야기 전달력'을 현재 작품이 충족하지 못하고 있음.
+**[제안 및 후속 조치]**
+1.  **콘텐츠 기획 검토 (Content Production):**
+    *   **비주얼 강화:** 음식이나 풍경 장면의 연출 및 촬영 방식을 전반적으로 재검토하여 시각적 완성도를 높일 필요가 있습니다. 특히 식음료(Food) 관련 콘텐츠는 디테일한 미장센과 색감 보정 등이 중요합니다.
+    *   **서사적 깊이 추가:** 단순히 '관찰'하는 수준을 넘어, 등장인물 간의 관계, 갈등, 혹은 문화적 맥락을 강화하는 등 스토리 라인의 재미를 강화해야 합니다.
+2.  **마케팅/홍보 방향 수정 (Marketing Strategy):**
+    *   기존의 스토리 중심 마케팅을 보완하여, **'음식의 미학'**이나 **'핀란드 고유의 자연 풍경'** 등 감성을 자극할 수 있는 시각적 요소를 강조하는 홍보 콘텐츠를 제작해야 합니다. (예: "느림의 미학", "핀란드의 겨울 색감" 등)
+    *   타 시청자에게 제공할 '보는 재미'에 대한 기대치를 높일 수 있는 티저 및 비하인드 콘텐츠를 활용해 사전 인지도를 높이는 방안을 검토해야 합니다.</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="F51" t="n">
+        <v>877</v>
+      </c>
+      <c r="G51" t="n">
+        <v>87.14</v>
+      </c>
+      <c r="H51" t="n">
         <v>6.11</v>
       </c>
     </row>
